--- a/public/downloads/client-growth.xlsx
+++ b/public/downloads/client-growth.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Account review" sheetId="1" r:id="R11073dae1b6f45dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily source" sheetId="2" r:id="R65dc1e34fa3842e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Account review" sheetId="1" r:id="R63a657c8e7fb497c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Daily source" sheetId="2" r:id="R721a5b298f014946"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -465,14 +465,14 @@
         <x:v>Current start</x:v>
       </x:c>
       <x:c r="B5" s="6" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="C5" s="2"/>
       <x:c r="D5" s="2" t="str">
         <x:v>Current end</x:v>
       </x:c>
       <x:c r="E5" s="6" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="F5" s="2"/>
       <x:c r="G5" s="2"/>
@@ -485,14 +485,14 @@
         <x:v>Prior start</x:v>
       </x:c>
       <x:c r="B6" s="6" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="C6" s="2"/>
       <x:c r="D6" s="2" t="str">
         <x:v>Prior end</x:v>
       </x:c>
       <x:c r="E6" s="6" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="F6" s="2"/>
       <x:c r="G6" s="2"/>
@@ -1373,7 +1373,7 @@
     </x:row>
     <x:row r="6" ht="20" customHeight="1">
       <x:c r="A6" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B6" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -1406,7 +1406,7 @@
     </x:row>
     <x:row r="7" ht="20" customHeight="1">
       <x:c r="A7" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B7" s="2" t="str">
         <x:v>Stride</x:v>
@@ -1439,7 +1439,7 @@
     </x:row>
     <x:row r="8" ht="20" customHeight="1">
       <x:c r="A8" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B8" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -1472,7 +1472,7 @@
     </x:row>
     <x:row r="9" ht="20" customHeight="1">
       <x:c r="A9" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B9" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -1505,7 +1505,7 @@
     </x:row>
     <x:row r="10" ht="20" customHeight="1">
       <x:c r="A10" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B10" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -1538,7 +1538,7 @@
     </x:row>
     <x:row r="11" ht="20" customHeight="1">
       <x:c r="A11" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B11" s="2" t="str">
         <x:v>Muse</x:v>
@@ -1571,7 +1571,7 @@
     </x:row>
     <x:row r="12" ht="20" customHeight="1">
       <x:c r="A12" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B12" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -1604,7 +1604,7 @@
     </x:row>
     <x:row r="13" ht="20" customHeight="1">
       <x:c r="A13" s="7" t="d">
-        <x:v>2026-06-23T12:00:00.000Z</x:v>
+        <x:v>2026-06-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B13" s="2" t="str">
         <x:v>Trail</x:v>
@@ -1637,7 +1637,7 @@
     </x:row>
     <x:row r="14" ht="20" customHeight="1">
       <x:c r="A14" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B14" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -1670,7 +1670,7 @@
     </x:row>
     <x:row r="15" ht="20" customHeight="1">
       <x:c r="A15" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B15" s="2" t="str">
         <x:v>Stride</x:v>
@@ -1703,7 +1703,7 @@
     </x:row>
     <x:row r="16" ht="20" customHeight="1">
       <x:c r="A16" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B16" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -1736,7 +1736,7 @@
     </x:row>
     <x:row r="17" ht="20" customHeight="1">
       <x:c r="A17" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B17" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -1769,7 +1769,7 @@
     </x:row>
     <x:row r="18" ht="20" customHeight="1">
       <x:c r="A18" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B18" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -1802,7 +1802,7 @@
     </x:row>
     <x:row r="19" ht="20" customHeight="1">
       <x:c r="A19" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B19" s="2" t="str">
         <x:v>Muse</x:v>
@@ -1835,7 +1835,7 @@
     </x:row>
     <x:row r="20" ht="20" customHeight="1">
       <x:c r="A20" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B20" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -1868,7 +1868,7 @@
     </x:row>
     <x:row r="21" ht="20" customHeight="1">
       <x:c r="A21" s="7" t="d">
-        <x:v>2026-06-24T12:00:00.000Z</x:v>
+        <x:v>2026-06-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B21" s="2" t="str">
         <x:v>Trail</x:v>
@@ -1901,7 +1901,7 @@
     </x:row>
     <x:row r="22" ht="20" customHeight="1">
       <x:c r="A22" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B22" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -1934,7 +1934,7 @@
     </x:row>
     <x:row r="23" ht="20" customHeight="1">
       <x:c r="A23" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B23" s="2" t="str">
         <x:v>Stride</x:v>
@@ -1967,7 +1967,7 @@
     </x:row>
     <x:row r="24" ht="20" customHeight="1">
       <x:c r="A24" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B24" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -2000,7 +2000,7 @@
     </x:row>
     <x:row r="25" ht="20" customHeight="1">
       <x:c r="A25" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B25" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -2033,7 +2033,7 @@
     </x:row>
     <x:row r="26" ht="20" customHeight="1">
       <x:c r="A26" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B26" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -2066,7 +2066,7 @@
     </x:row>
     <x:row r="27" ht="20" customHeight="1">
       <x:c r="A27" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B27" s="2" t="str">
         <x:v>Muse</x:v>
@@ -2099,7 +2099,7 @@
     </x:row>
     <x:row r="28" ht="20" customHeight="1">
       <x:c r="A28" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B28" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -2132,7 +2132,7 @@
     </x:row>
     <x:row r="29" ht="20" customHeight="1">
       <x:c r="A29" s="7" t="d">
-        <x:v>2026-06-25T12:00:00.000Z</x:v>
+        <x:v>2026-06-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B29" s="2" t="str">
         <x:v>Trail</x:v>
@@ -2165,7 +2165,7 @@
     </x:row>
     <x:row r="30" ht="20" customHeight="1">
       <x:c r="A30" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B30" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -2198,7 +2198,7 @@
     </x:row>
     <x:row r="31" ht="20" customHeight="1">
       <x:c r="A31" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B31" s="2" t="str">
         <x:v>Stride</x:v>
@@ -2231,7 +2231,7 @@
     </x:row>
     <x:row r="32" ht="20" customHeight="1">
       <x:c r="A32" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B32" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -2264,7 +2264,7 @@
     </x:row>
     <x:row r="33" ht="20" customHeight="1">
       <x:c r="A33" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B33" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -2297,7 +2297,7 @@
     </x:row>
     <x:row r="34" ht="20" customHeight="1">
       <x:c r="A34" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B34" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -2330,7 +2330,7 @@
     </x:row>
     <x:row r="35" ht="20" customHeight="1">
       <x:c r="A35" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B35" s="2" t="str">
         <x:v>Muse</x:v>
@@ -2363,7 +2363,7 @@
     </x:row>
     <x:row r="36" ht="20" customHeight="1">
       <x:c r="A36" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B36" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -2396,7 +2396,7 @@
     </x:row>
     <x:row r="37" ht="20" customHeight="1">
       <x:c r="A37" s="7" t="d">
-        <x:v>2026-06-26T12:00:00.000Z</x:v>
+        <x:v>2026-06-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B37" s="2" t="str">
         <x:v>Trail</x:v>
@@ -2429,7 +2429,7 @@
     </x:row>
     <x:row r="38" ht="20" customHeight="1">
       <x:c r="A38" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B38" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -2462,7 +2462,7 @@
     </x:row>
     <x:row r="39" ht="20" customHeight="1">
       <x:c r="A39" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B39" s="2" t="str">
         <x:v>Stride</x:v>
@@ -2495,7 +2495,7 @@
     </x:row>
     <x:row r="40" ht="20" customHeight="1">
       <x:c r="A40" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B40" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -2528,7 +2528,7 @@
     </x:row>
     <x:row r="41" ht="20" customHeight="1">
       <x:c r="A41" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B41" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -2561,7 +2561,7 @@
     </x:row>
     <x:row r="42" ht="20" customHeight="1">
       <x:c r="A42" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B42" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -2594,7 +2594,7 @@
     </x:row>
     <x:row r="43" ht="20" customHeight="1">
       <x:c r="A43" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B43" s="2" t="str">
         <x:v>Muse</x:v>
@@ -2627,7 +2627,7 @@
     </x:row>
     <x:row r="44" ht="20" customHeight="1">
       <x:c r="A44" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B44" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -2660,7 +2660,7 @@
     </x:row>
     <x:row r="45" ht="20" customHeight="1">
       <x:c r="A45" s="7" t="d">
-        <x:v>2026-06-27T12:00:00.000Z</x:v>
+        <x:v>2026-06-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B45" s="2" t="str">
         <x:v>Trail</x:v>
@@ -2693,7 +2693,7 @@
     </x:row>
     <x:row r="46" ht="20" customHeight="1">
       <x:c r="A46" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B46" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -2726,7 +2726,7 @@
     </x:row>
     <x:row r="47" ht="20" customHeight="1">
       <x:c r="A47" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B47" s="2" t="str">
         <x:v>Stride</x:v>
@@ -2759,7 +2759,7 @@
     </x:row>
     <x:row r="48" ht="20" customHeight="1">
       <x:c r="A48" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B48" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -2792,7 +2792,7 @@
     </x:row>
     <x:row r="49" ht="20" customHeight="1">
       <x:c r="A49" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B49" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -2825,7 +2825,7 @@
     </x:row>
     <x:row r="50" ht="20" customHeight="1">
       <x:c r="A50" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B50" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -2858,7 +2858,7 @@
     </x:row>
     <x:row r="51" ht="20" customHeight="1">
       <x:c r="A51" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B51" s="2" t="str">
         <x:v>Muse</x:v>
@@ -2891,7 +2891,7 @@
     </x:row>
     <x:row r="52" ht="20" customHeight="1">
       <x:c r="A52" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B52" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -2924,7 +2924,7 @@
     </x:row>
     <x:row r="53" ht="20" customHeight="1">
       <x:c r="A53" s="7" t="d">
-        <x:v>2026-06-28T12:00:00.000Z</x:v>
+        <x:v>2026-06-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B53" s="2" t="str">
         <x:v>Trail</x:v>
@@ -2957,7 +2957,7 @@
     </x:row>
     <x:row r="54" ht="20" customHeight="1">
       <x:c r="A54" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B54" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -2990,7 +2990,7 @@
     </x:row>
     <x:row r="55" ht="20" customHeight="1">
       <x:c r="A55" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B55" s="2" t="str">
         <x:v>Stride</x:v>
@@ -3023,7 +3023,7 @@
     </x:row>
     <x:row r="56" ht="20" customHeight="1">
       <x:c r="A56" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B56" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -3056,7 +3056,7 @@
     </x:row>
     <x:row r="57" ht="20" customHeight="1">
       <x:c r="A57" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B57" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -3089,7 +3089,7 @@
     </x:row>
     <x:row r="58" ht="20" customHeight="1">
       <x:c r="A58" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B58" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -3122,7 +3122,7 @@
     </x:row>
     <x:row r="59" ht="20" customHeight="1">
       <x:c r="A59" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B59" s="2" t="str">
         <x:v>Muse</x:v>
@@ -3155,7 +3155,7 @@
     </x:row>
     <x:row r="60" ht="20" customHeight="1">
       <x:c r="A60" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B60" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -3188,7 +3188,7 @@
     </x:row>
     <x:row r="61" ht="20" customHeight="1">
       <x:c r="A61" s="7" t="d">
-        <x:v>2026-06-29T12:00:00.000Z</x:v>
+        <x:v>2026-06-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B61" s="2" t="str">
         <x:v>Trail</x:v>
@@ -3221,7 +3221,7 @@
     </x:row>
     <x:row r="62" ht="20" customHeight="1">
       <x:c r="A62" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B62" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -3254,7 +3254,7 @@
     </x:row>
     <x:row r="63" ht="20" customHeight="1">
       <x:c r="A63" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B63" s="2" t="str">
         <x:v>Stride</x:v>
@@ -3287,7 +3287,7 @@
     </x:row>
     <x:row r="64" ht="20" customHeight="1">
       <x:c r="A64" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B64" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -3320,7 +3320,7 @@
     </x:row>
     <x:row r="65" ht="20" customHeight="1">
       <x:c r="A65" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B65" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -3353,7 +3353,7 @@
     </x:row>
     <x:row r="66" ht="20" customHeight="1">
       <x:c r="A66" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B66" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -3386,7 +3386,7 @@
     </x:row>
     <x:row r="67" ht="20" customHeight="1">
       <x:c r="A67" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B67" s="2" t="str">
         <x:v>Muse</x:v>
@@ -3419,7 +3419,7 @@
     </x:row>
     <x:row r="68" ht="20" customHeight="1">
       <x:c r="A68" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B68" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -3452,7 +3452,7 @@
     </x:row>
     <x:row r="69" ht="20" customHeight="1">
       <x:c r="A69" s="7" t="d">
-        <x:v>2026-06-30T12:00:00.000Z</x:v>
+        <x:v>2026-06-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B69" s="2" t="str">
         <x:v>Trail</x:v>
@@ -3485,7 +3485,7 @@
     </x:row>
     <x:row r="70" ht="20" customHeight="1">
       <x:c r="A70" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B70" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -3518,7 +3518,7 @@
     </x:row>
     <x:row r="71" ht="20" customHeight="1">
       <x:c r="A71" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B71" s="2" t="str">
         <x:v>Stride</x:v>
@@ -3551,7 +3551,7 @@
     </x:row>
     <x:row r="72" ht="20" customHeight="1">
       <x:c r="A72" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B72" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -3584,7 +3584,7 @@
     </x:row>
     <x:row r="73" ht="20" customHeight="1">
       <x:c r="A73" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B73" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -3617,7 +3617,7 @@
     </x:row>
     <x:row r="74" ht="20" customHeight="1">
       <x:c r="A74" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B74" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -3650,7 +3650,7 @@
     </x:row>
     <x:row r="75" ht="20" customHeight="1">
       <x:c r="A75" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B75" s="2" t="str">
         <x:v>Muse</x:v>
@@ -3683,7 +3683,7 @@
     </x:row>
     <x:row r="76" ht="20" customHeight="1">
       <x:c r="A76" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B76" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -3716,7 +3716,7 @@
     </x:row>
     <x:row r="77" ht="20" customHeight="1">
       <x:c r="A77" s="7" t="d">
-        <x:v>2026-07-01T12:00:00.000Z</x:v>
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B77" s="2" t="str">
         <x:v>Trail</x:v>
@@ -3749,7 +3749,7 @@
     </x:row>
     <x:row r="78" ht="20" customHeight="1">
       <x:c r="A78" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B78" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -3782,7 +3782,7 @@
     </x:row>
     <x:row r="79" ht="20" customHeight="1">
       <x:c r="A79" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B79" s="2" t="str">
         <x:v>Stride</x:v>
@@ -3815,7 +3815,7 @@
     </x:row>
     <x:row r="80" ht="20" customHeight="1">
       <x:c r="A80" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B80" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -3848,7 +3848,7 @@
     </x:row>
     <x:row r="81" ht="20" customHeight="1">
       <x:c r="A81" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B81" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -3881,7 +3881,7 @@
     </x:row>
     <x:row r="82" ht="20" customHeight="1">
       <x:c r="A82" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B82" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -3914,7 +3914,7 @@
     </x:row>
     <x:row r="83" ht="20" customHeight="1">
       <x:c r="A83" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B83" s="2" t="str">
         <x:v>Muse</x:v>
@@ -3947,7 +3947,7 @@
     </x:row>
     <x:row r="84" ht="20" customHeight="1">
       <x:c r="A84" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B84" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -3980,7 +3980,7 @@
     </x:row>
     <x:row r="85" ht="20" customHeight="1">
       <x:c r="A85" s="7" t="d">
-        <x:v>2026-07-02T12:00:00.000Z</x:v>
+        <x:v>2026-07-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B85" s="2" t="str">
         <x:v>Trail</x:v>
@@ -4013,7 +4013,7 @@
     </x:row>
     <x:row r="86" ht="20" customHeight="1">
       <x:c r="A86" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B86" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -4046,7 +4046,7 @@
     </x:row>
     <x:row r="87" ht="20" customHeight="1">
       <x:c r="A87" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B87" s="2" t="str">
         <x:v>Stride</x:v>
@@ -4079,7 +4079,7 @@
     </x:row>
     <x:row r="88" ht="20" customHeight="1">
       <x:c r="A88" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B88" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -4112,7 +4112,7 @@
     </x:row>
     <x:row r="89" ht="20" customHeight="1">
       <x:c r="A89" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B89" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -4145,7 +4145,7 @@
     </x:row>
     <x:row r="90" ht="20" customHeight="1">
       <x:c r="A90" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B90" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -4178,7 +4178,7 @@
     </x:row>
     <x:row r="91" ht="20" customHeight="1">
       <x:c r="A91" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B91" s="2" t="str">
         <x:v>Muse</x:v>
@@ -4211,7 +4211,7 @@
     </x:row>
     <x:row r="92" ht="20" customHeight="1">
       <x:c r="A92" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B92" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -4244,7 +4244,7 @@
     </x:row>
     <x:row r="93" ht="20" customHeight="1">
       <x:c r="A93" s="7" t="d">
-        <x:v>2026-07-03T12:00:00.000Z</x:v>
+        <x:v>2026-07-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B93" s="2" t="str">
         <x:v>Trail</x:v>
@@ -4277,7 +4277,7 @@
     </x:row>
     <x:row r="94" ht="20" customHeight="1">
       <x:c r="A94" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B94" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -4310,7 +4310,7 @@
     </x:row>
     <x:row r="95" ht="20" customHeight="1">
       <x:c r="A95" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B95" s="2" t="str">
         <x:v>Stride</x:v>
@@ -4343,7 +4343,7 @@
     </x:row>
     <x:row r="96" ht="20" customHeight="1">
       <x:c r="A96" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B96" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -4376,7 +4376,7 @@
     </x:row>
     <x:row r="97" ht="20" customHeight="1">
       <x:c r="A97" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B97" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -4409,7 +4409,7 @@
     </x:row>
     <x:row r="98" ht="20" customHeight="1">
       <x:c r="A98" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B98" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -4442,7 +4442,7 @@
     </x:row>
     <x:row r="99" ht="20" customHeight="1">
       <x:c r="A99" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B99" s="2" t="str">
         <x:v>Muse</x:v>
@@ -4475,7 +4475,7 @@
     </x:row>
     <x:row r="100" ht="20" customHeight="1">
       <x:c r="A100" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B100" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -4508,7 +4508,7 @@
     </x:row>
     <x:row r="101" ht="20" customHeight="1">
       <x:c r="A101" s="7" t="d">
-        <x:v>2026-07-04T12:00:00.000Z</x:v>
+        <x:v>2026-07-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B101" s="2" t="str">
         <x:v>Trail</x:v>
@@ -4541,7 +4541,7 @@
     </x:row>
     <x:row r="102" ht="20" customHeight="1">
       <x:c r="A102" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B102" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -4574,7 +4574,7 @@
     </x:row>
     <x:row r="103" ht="20" customHeight="1">
       <x:c r="A103" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B103" s="2" t="str">
         <x:v>Stride</x:v>
@@ -4607,7 +4607,7 @@
     </x:row>
     <x:row r="104" ht="20" customHeight="1">
       <x:c r="A104" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B104" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -4640,7 +4640,7 @@
     </x:row>
     <x:row r="105" ht="20" customHeight="1">
       <x:c r="A105" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B105" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -4673,7 +4673,7 @@
     </x:row>
     <x:row r="106" ht="20" customHeight="1">
       <x:c r="A106" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B106" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -4706,7 +4706,7 @@
     </x:row>
     <x:row r="107" ht="20" customHeight="1">
       <x:c r="A107" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B107" s="2" t="str">
         <x:v>Muse</x:v>
@@ -4739,7 +4739,7 @@
     </x:row>
     <x:row r="108" ht="20" customHeight="1">
       <x:c r="A108" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B108" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -4772,7 +4772,7 @@
     </x:row>
     <x:row r="109" ht="20" customHeight="1">
       <x:c r="A109" s="7" t="d">
-        <x:v>2026-07-05T12:00:00.000Z</x:v>
+        <x:v>2026-07-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B109" s="2" t="str">
         <x:v>Trail</x:v>
@@ -4805,7 +4805,7 @@
     </x:row>
     <x:row r="110" ht="20" customHeight="1">
       <x:c r="A110" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B110" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -4838,7 +4838,7 @@
     </x:row>
     <x:row r="111" ht="20" customHeight="1">
       <x:c r="A111" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B111" s="2" t="str">
         <x:v>Stride</x:v>
@@ -4871,7 +4871,7 @@
     </x:row>
     <x:row r="112" ht="20" customHeight="1">
       <x:c r="A112" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B112" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -4904,7 +4904,7 @@
     </x:row>
     <x:row r="113" ht="20" customHeight="1">
       <x:c r="A113" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B113" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -4937,7 +4937,7 @@
     </x:row>
     <x:row r="114" ht="20" customHeight="1">
       <x:c r="A114" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B114" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -4970,7 +4970,7 @@
     </x:row>
     <x:row r="115" ht="20" customHeight="1">
       <x:c r="A115" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B115" s="2" t="str">
         <x:v>Muse</x:v>
@@ -5003,7 +5003,7 @@
     </x:row>
     <x:row r="116" ht="20" customHeight="1">
       <x:c r="A116" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B116" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -5036,7 +5036,7 @@
     </x:row>
     <x:row r="117" ht="20" customHeight="1">
       <x:c r="A117" s="7" t="d">
-        <x:v>2026-07-06T12:00:00.000Z</x:v>
+        <x:v>2026-07-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B117" s="2" t="str">
         <x:v>Trail</x:v>
@@ -5069,7 +5069,7 @@
     </x:row>
     <x:row r="118" ht="20" customHeight="1">
       <x:c r="A118" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B118" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -5102,7 +5102,7 @@
     </x:row>
     <x:row r="119" ht="20" customHeight="1">
       <x:c r="A119" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B119" s="2" t="str">
         <x:v>Stride</x:v>
@@ -5135,7 +5135,7 @@
     </x:row>
     <x:row r="120" ht="20" customHeight="1">
       <x:c r="A120" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B120" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -5168,7 +5168,7 @@
     </x:row>
     <x:row r="121" ht="20" customHeight="1">
       <x:c r="A121" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B121" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -5201,7 +5201,7 @@
     </x:row>
     <x:row r="122" ht="20" customHeight="1">
       <x:c r="A122" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B122" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -5234,7 +5234,7 @@
     </x:row>
     <x:row r="123" ht="20" customHeight="1">
       <x:c r="A123" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B123" s="2" t="str">
         <x:v>Muse</x:v>
@@ -5267,7 +5267,7 @@
     </x:row>
     <x:row r="124" ht="20" customHeight="1">
       <x:c r="A124" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B124" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -5300,7 +5300,7 @@
     </x:row>
     <x:row r="125" ht="20" customHeight="1">
       <x:c r="A125" s="7" t="d">
-        <x:v>2026-07-07T12:00:00.000Z</x:v>
+        <x:v>2026-07-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B125" s="2" t="str">
         <x:v>Trail</x:v>
@@ -5333,7 +5333,7 @@
     </x:row>
     <x:row r="126" ht="20" customHeight="1">
       <x:c r="A126" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B126" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -5366,7 +5366,7 @@
     </x:row>
     <x:row r="127" ht="20" customHeight="1">
       <x:c r="A127" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B127" s="2" t="str">
         <x:v>Stride</x:v>
@@ -5399,7 +5399,7 @@
     </x:row>
     <x:row r="128" ht="20" customHeight="1">
       <x:c r="A128" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B128" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -5432,7 +5432,7 @@
     </x:row>
     <x:row r="129" ht="20" customHeight="1">
       <x:c r="A129" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B129" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -5465,7 +5465,7 @@
     </x:row>
     <x:row r="130" ht="20" customHeight="1">
       <x:c r="A130" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B130" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -5498,7 +5498,7 @@
     </x:row>
     <x:row r="131" ht="20" customHeight="1">
       <x:c r="A131" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B131" s="2" t="str">
         <x:v>Muse</x:v>
@@ -5531,7 +5531,7 @@
     </x:row>
     <x:row r="132" ht="20" customHeight="1">
       <x:c r="A132" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B132" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -5564,7 +5564,7 @@
     </x:row>
     <x:row r="133" ht="20" customHeight="1">
       <x:c r="A133" s="7" t="d">
-        <x:v>2026-07-08T12:00:00.000Z</x:v>
+        <x:v>2026-07-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B133" s="2" t="str">
         <x:v>Trail</x:v>
@@ -5597,7 +5597,7 @@
     </x:row>
     <x:row r="134" ht="20" customHeight="1">
       <x:c r="A134" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B134" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -5630,7 +5630,7 @@
     </x:row>
     <x:row r="135" ht="20" customHeight="1">
       <x:c r="A135" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B135" s="2" t="str">
         <x:v>Stride</x:v>
@@ -5663,7 +5663,7 @@
     </x:row>
     <x:row r="136" ht="20" customHeight="1">
       <x:c r="A136" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B136" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -5696,7 +5696,7 @@
     </x:row>
     <x:row r="137" ht="20" customHeight="1">
       <x:c r="A137" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B137" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -5729,7 +5729,7 @@
     </x:row>
     <x:row r="138" ht="20" customHeight="1">
       <x:c r="A138" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B138" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -5762,7 +5762,7 @@
     </x:row>
     <x:row r="139" ht="20" customHeight="1">
       <x:c r="A139" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B139" s="2" t="str">
         <x:v>Muse</x:v>
@@ -5795,7 +5795,7 @@
     </x:row>
     <x:row r="140" ht="20" customHeight="1">
       <x:c r="A140" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B140" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -5828,7 +5828,7 @@
     </x:row>
     <x:row r="141" ht="20" customHeight="1">
       <x:c r="A141" s="7" t="d">
-        <x:v>2026-07-09T12:00:00.000Z</x:v>
+        <x:v>2026-07-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B141" s="2" t="str">
         <x:v>Trail</x:v>
@@ -5861,7 +5861,7 @@
     </x:row>
     <x:row r="142" ht="20" customHeight="1">
       <x:c r="A142" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B142" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -5894,7 +5894,7 @@
     </x:row>
     <x:row r="143" ht="20" customHeight="1">
       <x:c r="A143" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B143" s="2" t="str">
         <x:v>Stride</x:v>
@@ -5927,7 +5927,7 @@
     </x:row>
     <x:row r="144" ht="20" customHeight="1">
       <x:c r="A144" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B144" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -5960,7 +5960,7 @@
     </x:row>
     <x:row r="145" ht="20" customHeight="1">
       <x:c r="A145" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B145" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -5993,7 +5993,7 @@
     </x:row>
     <x:row r="146" ht="20" customHeight="1">
       <x:c r="A146" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B146" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -6026,7 +6026,7 @@
     </x:row>
     <x:row r="147" ht="20" customHeight="1">
       <x:c r="A147" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B147" s="2" t="str">
         <x:v>Muse</x:v>
@@ -6059,7 +6059,7 @@
     </x:row>
     <x:row r="148" ht="20" customHeight="1">
       <x:c r="A148" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B148" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -6092,7 +6092,7 @@
     </x:row>
     <x:row r="149" ht="20" customHeight="1">
       <x:c r="A149" s="7" t="d">
-        <x:v>2026-07-10T12:00:00.000Z</x:v>
+        <x:v>2026-07-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B149" s="2" t="str">
         <x:v>Trail</x:v>
@@ -6125,7 +6125,7 @@
     </x:row>
     <x:row r="150" ht="20" customHeight="1">
       <x:c r="A150" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B150" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -6158,7 +6158,7 @@
     </x:row>
     <x:row r="151" ht="20" customHeight="1">
       <x:c r="A151" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B151" s="2" t="str">
         <x:v>Stride</x:v>
@@ -6191,7 +6191,7 @@
     </x:row>
     <x:row r="152" ht="20" customHeight="1">
       <x:c r="A152" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B152" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -6224,7 +6224,7 @@
     </x:row>
     <x:row r="153" ht="20" customHeight="1">
       <x:c r="A153" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B153" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -6257,7 +6257,7 @@
     </x:row>
     <x:row r="154" ht="20" customHeight="1">
       <x:c r="A154" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B154" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -6290,7 +6290,7 @@
     </x:row>
     <x:row r="155" ht="20" customHeight="1">
       <x:c r="A155" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B155" s="2" t="str">
         <x:v>Muse</x:v>
@@ -6323,7 +6323,7 @@
     </x:row>
     <x:row r="156" ht="20" customHeight="1">
       <x:c r="A156" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B156" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -6356,7 +6356,7 @@
     </x:row>
     <x:row r="157" ht="20" customHeight="1">
       <x:c r="A157" s="7" t="d">
-        <x:v>2026-07-11T12:00:00.000Z</x:v>
+        <x:v>2026-07-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B157" s="2" t="str">
         <x:v>Trail</x:v>
@@ -6389,7 +6389,7 @@
     </x:row>
     <x:row r="158" ht="20" customHeight="1">
       <x:c r="A158" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B158" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -6422,7 +6422,7 @@
     </x:row>
     <x:row r="159" ht="20" customHeight="1">
       <x:c r="A159" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B159" s="2" t="str">
         <x:v>Stride</x:v>
@@ -6455,7 +6455,7 @@
     </x:row>
     <x:row r="160" ht="20" customHeight="1">
       <x:c r="A160" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B160" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -6488,7 +6488,7 @@
     </x:row>
     <x:row r="161" ht="20" customHeight="1">
       <x:c r="A161" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B161" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -6521,7 +6521,7 @@
     </x:row>
     <x:row r="162" ht="20" customHeight="1">
       <x:c r="A162" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B162" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -6554,7 +6554,7 @@
     </x:row>
     <x:row r="163" ht="20" customHeight="1">
       <x:c r="A163" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B163" s="2" t="str">
         <x:v>Muse</x:v>
@@ -6587,7 +6587,7 @@
     </x:row>
     <x:row r="164" ht="20" customHeight="1">
       <x:c r="A164" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B164" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -6620,7 +6620,7 @@
     </x:row>
     <x:row r="165" ht="20" customHeight="1">
       <x:c r="A165" s="7" t="d">
-        <x:v>2026-07-12T12:00:00.000Z</x:v>
+        <x:v>2026-07-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B165" s="2" t="str">
         <x:v>Trail</x:v>
@@ -6653,7 +6653,7 @@
     </x:row>
     <x:row r="166" ht="20" customHeight="1">
       <x:c r="A166" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B166" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -6686,7 +6686,7 @@
     </x:row>
     <x:row r="167" ht="20" customHeight="1">
       <x:c r="A167" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B167" s="2" t="str">
         <x:v>Stride</x:v>
@@ -6719,7 +6719,7 @@
     </x:row>
     <x:row r="168" ht="20" customHeight="1">
       <x:c r="A168" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B168" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -6752,7 +6752,7 @@
     </x:row>
     <x:row r="169" ht="20" customHeight="1">
       <x:c r="A169" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B169" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -6785,7 +6785,7 @@
     </x:row>
     <x:row r="170" ht="20" customHeight="1">
       <x:c r="A170" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B170" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -6818,7 +6818,7 @@
     </x:row>
     <x:row r="171" ht="20" customHeight="1">
       <x:c r="A171" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B171" s="2" t="str">
         <x:v>Muse</x:v>
@@ -6851,7 +6851,7 @@
     </x:row>
     <x:row r="172" ht="20" customHeight="1">
       <x:c r="A172" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B172" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -6884,7 +6884,7 @@
     </x:row>
     <x:row r="173" ht="20" customHeight="1">
       <x:c r="A173" s="7" t="d">
-        <x:v>2026-07-13T12:00:00.000Z</x:v>
+        <x:v>2026-07-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B173" s="2" t="str">
         <x:v>Trail</x:v>
@@ -6917,7 +6917,7 @@
     </x:row>
     <x:row r="174" ht="20" customHeight="1">
       <x:c r="A174" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B174" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -6950,7 +6950,7 @@
     </x:row>
     <x:row r="175" ht="20" customHeight="1">
       <x:c r="A175" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B175" s="2" t="str">
         <x:v>Stride</x:v>
@@ -6983,7 +6983,7 @@
     </x:row>
     <x:row r="176" ht="20" customHeight="1">
       <x:c r="A176" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B176" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -7016,7 +7016,7 @@
     </x:row>
     <x:row r="177" ht="20" customHeight="1">
       <x:c r="A177" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B177" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -7049,7 +7049,7 @@
     </x:row>
     <x:row r="178" ht="20" customHeight="1">
       <x:c r="A178" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B178" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -7082,7 +7082,7 @@
     </x:row>
     <x:row r="179" ht="20" customHeight="1">
       <x:c r="A179" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B179" s="2" t="str">
         <x:v>Muse</x:v>
@@ -7115,7 +7115,7 @@
     </x:row>
     <x:row r="180" ht="20" customHeight="1">
       <x:c r="A180" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B180" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -7148,7 +7148,7 @@
     </x:row>
     <x:row r="181" ht="20" customHeight="1">
       <x:c r="A181" s="7" t="d">
-        <x:v>2026-07-14T12:00:00.000Z</x:v>
+        <x:v>2026-07-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B181" s="2" t="str">
         <x:v>Trail</x:v>
@@ -7181,7 +7181,7 @@
     </x:row>
     <x:row r="182" ht="20" customHeight="1">
       <x:c r="A182" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B182" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -7214,7 +7214,7 @@
     </x:row>
     <x:row r="183" ht="20" customHeight="1">
       <x:c r="A183" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B183" s="2" t="str">
         <x:v>Stride</x:v>
@@ -7247,7 +7247,7 @@
     </x:row>
     <x:row r="184" ht="20" customHeight="1">
       <x:c r="A184" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B184" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -7280,7 +7280,7 @@
     </x:row>
     <x:row r="185" ht="20" customHeight="1">
       <x:c r="A185" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B185" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -7313,7 +7313,7 @@
     </x:row>
     <x:row r="186" ht="20" customHeight="1">
       <x:c r="A186" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B186" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -7346,7 +7346,7 @@
     </x:row>
     <x:row r="187" ht="20" customHeight="1">
       <x:c r="A187" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B187" s="2" t="str">
         <x:v>Muse</x:v>
@@ -7379,7 +7379,7 @@
     </x:row>
     <x:row r="188" ht="20" customHeight="1">
       <x:c r="A188" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B188" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -7412,7 +7412,7 @@
     </x:row>
     <x:row r="189" ht="20" customHeight="1">
       <x:c r="A189" s="7" t="d">
-        <x:v>2026-07-15T12:00:00.000Z</x:v>
+        <x:v>2026-07-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B189" s="2" t="str">
         <x:v>Trail</x:v>
@@ -7445,7 +7445,7 @@
     </x:row>
     <x:row r="190" ht="20" customHeight="1">
       <x:c r="A190" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B190" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -7478,7 +7478,7 @@
     </x:row>
     <x:row r="191" ht="20" customHeight="1">
       <x:c r="A191" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B191" s="2" t="str">
         <x:v>Stride</x:v>
@@ -7511,7 +7511,7 @@
     </x:row>
     <x:row r="192" ht="20" customHeight="1">
       <x:c r="A192" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B192" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -7544,7 +7544,7 @@
     </x:row>
     <x:row r="193" ht="20" customHeight="1">
       <x:c r="A193" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B193" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -7577,7 +7577,7 @@
     </x:row>
     <x:row r="194" ht="20" customHeight="1">
       <x:c r="A194" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B194" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -7610,7 +7610,7 @@
     </x:row>
     <x:row r="195" ht="20" customHeight="1">
       <x:c r="A195" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B195" s="2" t="str">
         <x:v>Muse</x:v>
@@ -7643,7 +7643,7 @@
     </x:row>
     <x:row r="196" ht="20" customHeight="1">
       <x:c r="A196" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B196" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -7676,7 +7676,7 @@
     </x:row>
     <x:row r="197" ht="20" customHeight="1">
       <x:c r="A197" s="7" t="d">
-        <x:v>2026-07-16T12:00:00.000Z</x:v>
+        <x:v>2026-07-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B197" s="2" t="str">
         <x:v>Trail</x:v>
@@ -7709,7 +7709,7 @@
     </x:row>
     <x:row r="198" ht="20" customHeight="1">
       <x:c r="A198" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B198" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -7742,7 +7742,7 @@
     </x:row>
     <x:row r="199" ht="20" customHeight="1">
       <x:c r="A199" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B199" s="2" t="str">
         <x:v>Stride</x:v>
@@ -7775,7 +7775,7 @@
     </x:row>
     <x:row r="200" ht="20" customHeight="1">
       <x:c r="A200" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B200" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -7808,7 +7808,7 @@
     </x:row>
     <x:row r="201" ht="20" customHeight="1">
       <x:c r="A201" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B201" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -7841,7 +7841,7 @@
     </x:row>
     <x:row r="202" ht="20" customHeight="1">
       <x:c r="A202" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B202" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -7874,7 +7874,7 @@
     </x:row>
     <x:row r="203" ht="20" customHeight="1">
       <x:c r="A203" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B203" s="2" t="str">
         <x:v>Muse</x:v>
@@ -7907,7 +7907,7 @@
     </x:row>
     <x:row r="204" ht="20" customHeight="1">
       <x:c r="A204" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B204" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -7940,7 +7940,7 @@
     </x:row>
     <x:row r="205" ht="20" customHeight="1">
       <x:c r="A205" s="7" t="d">
-        <x:v>2026-07-17T12:00:00.000Z</x:v>
+        <x:v>2026-07-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B205" s="2" t="str">
         <x:v>Trail</x:v>
@@ -7973,7 +7973,7 @@
     </x:row>
     <x:row r="206" ht="20" customHeight="1">
       <x:c r="A206" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B206" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -8006,7 +8006,7 @@
     </x:row>
     <x:row r="207" ht="20" customHeight="1">
       <x:c r="A207" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B207" s="2" t="str">
         <x:v>Stride</x:v>
@@ -8039,7 +8039,7 @@
     </x:row>
     <x:row r="208" ht="20" customHeight="1">
       <x:c r="A208" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B208" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -8072,7 +8072,7 @@
     </x:row>
     <x:row r="209" ht="20" customHeight="1">
       <x:c r="A209" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B209" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -8105,7 +8105,7 @@
     </x:row>
     <x:row r="210" ht="20" customHeight="1">
       <x:c r="A210" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B210" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -8138,7 +8138,7 @@
     </x:row>
     <x:row r="211" ht="20" customHeight="1">
       <x:c r="A211" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B211" s="2" t="str">
         <x:v>Muse</x:v>
@@ -8171,7 +8171,7 @@
     </x:row>
     <x:row r="212" ht="20" customHeight="1">
       <x:c r="A212" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B212" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -8204,7 +8204,7 @@
     </x:row>
     <x:row r="213" ht="20" customHeight="1">
       <x:c r="A213" s="7" t="d">
-        <x:v>2026-07-18T12:00:00.000Z</x:v>
+        <x:v>2026-07-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B213" s="2" t="str">
         <x:v>Trail</x:v>
@@ -8237,7 +8237,7 @@
     </x:row>
     <x:row r="214" ht="20" customHeight="1">
       <x:c r="A214" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B214" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -8270,7 +8270,7 @@
     </x:row>
     <x:row r="215" ht="20" customHeight="1">
       <x:c r="A215" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B215" s="2" t="str">
         <x:v>Stride</x:v>
@@ -8303,7 +8303,7 @@
     </x:row>
     <x:row r="216" ht="20" customHeight="1">
       <x:c r="A216" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B216" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -8336,7 +8336,7 @@
     </x:row>
     <x:row r="217" ht="20" customHeight="1">
       <x:c r="A217" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B217" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -8369,7 +8369,7 @@
     </x:row>
     <x:row r="218" ht="20" customHeight="1">
       <x:c r="A218" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B218" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -8402,7 +8402,7 @@
     </x:row>
     <x:row r="219" ht="20" customHeight="1">
       <x:c r="A219" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B219" s="2" t="str">
         <x:v>Muse</x:v>
@@ -8435,7 +8435,7 @@
     </x:row>
     <x:row r="220" ht="20" customHeight="1">
       <x:c r="A220" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B220" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -8468,7 +8468,7 @@
     </x:row>
     <x:row r="221" ht="20" customHeight="1">
       <x:c r="A221" s="7" t="d">
-        <x:v>2026-07-19T12:00:00.000Z</x:v>
+        <x:v>2026-07-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B221" s="2" t="str">
         <x:v>Trail</x:v>
@@ -8501,7 +8501,7 @@
     </x:row>
     <x:row r="222" ht="20" customHeight="1">
       <x:c r="A222" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B222" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -8534,7 +8534,7 @@
     </x:row>
     <x:row r="223" ht="20" customHeight="1">
       <x:c r="A223" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B223" s="2" t="str">
         <x:v>Stride</x:v>
@@ -8567,7 +8567,7 @@
     </x:row>
     <x:row r="224" ht="20" customHeight="1">
       <x:c r="A224" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B224" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -8600,7 +8600,7 @@
     </x:row>
     <x:row r="225" ht="20" customHeight="1">
       <x:c r="A225" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B225" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -8633,7 +8633,7 @@
     </x:row>
     <x:row r="226" ht="20" customHeight="1">
       <x:c r="A226" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B226" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -8666,7 +8666,7 @@
     </x:row>
     <x:row r="227" ht="20" customHeight="1">
       <x:c r="A227" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B227" s="2" t="str">
         <x:v>Muse</x:v>
@@ -8699,7 +8699,7 @@
     </x:row>
     <x:row r="228" ht="20" customHeight="1">
       <x:c r="A228" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B228" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -8732,7 +8732,7 @@
     </x:row>
     <x:row r="229" ht="20" customHeight="1">
       <x:c r="A229" s="7" t="d">
-        <x:v>2026-07-20T12:00:00.000Z</x:v>
+        <x:v>2026-07-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B229" s="2" t="str">
         <x:v>Trail</x:v>
@@ -8765,7 +8765,7 @@
     </x:row>
     <x:row r="230" ht="20" customHeight="1">
       <x:c r="A230" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B230" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -8798,7 +8798,7 @@
     </x:row>
     <x:row r="231" ht="20" customHeight="1">
       <x:c r="A231" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B231" s="2" t="str">
         <x:v>Stride</x:v>
@@ -8831,7 +8831,7 @@
     </x:row>
     <x:row r="232" ht="20" customHeight="1">
       <x:c r="A232" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B232" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -8864,7 +8864,7 @@
     </x:row>
     <x:row r="233" ht="20" customHeight="1">
       <x:c r="A233" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B233" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -8897,7 +8897,7 @@
     </x:row>
     <x:row r="234" ht="20" customHeight="1">
       <x:c r="A234" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B234" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -8930,7 +8930,7 @@
     </x:row>
     <x:row r="235" ht="20" customHeight="1">
       <x:c r="A235" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B235" s="2" t="str">
         <x:v>Muse</x:v>
@@ -8963,7 +8963,7 @@
     </x:row>
     <x:row r="236" ht="20" customHeight="1">
       <x:c r="A236" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B236" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -8996,7 +8996,7 @@
     </x:row>
     <x:row r="237" ht="20" customHeight="1">
       <x:c r="A237" s="7" t="d">
-        <x:v>2026-07-21T12:00:00.000Z</x:v>
+        <x:v>2026-07-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B237" s="2" t="str">
         <x:v>Trail</x:v>
@@ -9029,7 +9029,7 @@
     </x:row>
     <x:row r="238" ht="20" customHeight="1">
       <x:c r="A238" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B238" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -9062,7 +9062,7 @@
     </x:row>
     <x:row r="239" ht="20" customHeight="1">
       <x:c r="A239" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B239" s="2" t="str">
         <x:v>Stride</x:v>
@@ -9095,7 +9095,7 @@
     </x:row>
     <x:row r="240" ht="20" customHeight="1">
       <x:c r="A240" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B240" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -9128,7 +9128,7 @@
     </x:row>
     <x:row r="241" ht="20" customHeight="1">
       <x:c r="A241" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B241" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -9161,7 +9161,7 @@
     </x:row>
     <x:row r="242" ht="20" customHeight="1">
       <x:c r="A242" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B242" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -9194,7 +9194,7 @@
     </x:row>
     <x:row r="243" ht="20" customHeight="1">
       <x:c r="A243" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B243" s="2" t="str">
         <x:v>Muse</x:v>
@@ -9227,7 +9227,7 @@
     </x:row>
     <x:row r="244" ht="20" customHeight="1">
       <x:c r="A244" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B244" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -9260,7 +9260,7 @@
     </x:row>
     <x:row r="245" ht="20" customHeight="1">
       <x:c r="A245" s="7" t="d">
-        <x:v>2026-07-22T12:00:00.000Z</x:v>
+        <x:v>2026-07-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B245" s="2" t="str">
         <x:v>Trail</x:v>
@@ -9293,7 +9293,7 @@
     </x:row>
     <x:row r="246" ht="20" customHeight="1">
       <x:c r="A246" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B246" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -9326,7 +9326,7 @@
     </x:row>
     <x:row r="247" ht="20" customHeight="1">
       <x:c r="A247" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B247" s="2" t="str">
         <x:v>Stride</x:v>
@@ -9359,7 +9359,7 @@
     </x:row>
     <x:row r="248" ht="20" customHeight="1">
       <x:c r="A248" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B248" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -9392,7 +9392,7 @@
     </x:row>
     <x:row r="249" ht="20" customHeight="1">
       <x:c r="A249" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B249" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -9425,7 +9425,7 @@
     </x:row>
     <x:row r="250" ht="20" customHeight="1">
       <x:c r="A250" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B250" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -9458,7 +9458,7 @@
     </x:row>
     <x:row r="251" ht="20" customHeight="1">
       <x:c r="A251" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B251" s="2" t="str">
         <x:v>Muse</x:v>
@@ -9491,7 +9491,7 @@
     </x:row>
     <x:row r="252" ht="20" customHeight="1">
       <x:c r="A252" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B252" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -9524,7 +9524,7 @@
     </x:row>
     <x:row r="253" ht="20" customHeight="1">
       <x:c r="A253" s="7" t="d">
-        <x:v>2026-07-23T12:00:00.000Z</x:v>
+        <x:v>2026-07-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B253" s="2" t="str">
         <x:v>Trail</x:v>
@@ -9557,7 +9557,7 @@
     </x:row>
     <x:row r="254" ht="20" customHeight="1">
       <x:c r="A254" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B254" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -9590,7 +9590,7 @@
     </x:row>
     <x:row r="255" ht="20" customHeight="1">
       <x:c r="A255" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B255" s="2" t="str">
         <x:v>Stride</x:v>
@@ -9623,7 +9623,7 @@
     </x:row>
     <x:row r="256" ht="20" customHeight="1">
       <x:c r="A256" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B256" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -9656,7 +9656,7 @@
     </x:row>
     <x:row r="257" ht="20" customHeight="1">
       <x:c r="A257" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B257" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -9689,7 +9689,7 @@
     </x:row>
     <x:row r="258" ht="20" customHeight="1">
       <x:c r="A258" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B258" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -9722,7 +9722,7 @@
     </x:row>
     <x:row r="259" ht="20" customHeight="1">
       <x:c r="A259" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B259" s="2" t="str">
         <x:v>Muse</x:v>
@@ -9755,7 +9755,7 @@
     </x:row>
     <x:row r="260" ht="20" customHeight="1">
       <x:c r="A260" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B260" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -9788,7 +9788,7 @@
     </x:row>
     <x:row r="261" ht="20" customHeight="1">
       <x:c r="A261" s="7" t="d">
-        <x:v>2026-07-24T12:00:00.000Z</x:v>
+        <x:v>2026-07-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B261" s="2" t="str">
         <x:v>Trail</x:v>
@@ -9821,7 +9821,7 @@
     </x:row>
     <x:row r="262" ht="20" customHeight="1">
       <x:c r="A262" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B262" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -9854,7 +9854,7 @@
     </x:row>
     <x:row r="263" ht="20" customHeight="1">
       <x:c r="A263" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B263" s="2" t="str">
         <x:v>Stride</x:v>
@@ -9887,7 +9887,7 @@
     </x:row>
     <x:row r="264" ht="20" customHeight="1">
       <x:c r="A264" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B264" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -9920,7 +9920,7 @@
     </x:row>
     <x:row r="265" ht="20" customHeight="1">
       <x:c r="A265" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B265" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -9953,7 +9953,7 @@
     </x:row>
     <x:row r="266" ht="20" customHeight="1">
       <x:c r="A266" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B266" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -9986,7 +9986,7 @@
     </x:row>
     <x:row r="267" ht="20" customHeight="1">
       <x:c r="A267" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B267" s="2" t="str">
         <x:v>Muse</x:v>
@@ -10019,7 +10019,7 @@
     </x:row>
     <x:row r="268" ht="20" customHeight="1">
       <x:c r="A268" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B268" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -10052,7 +10052,7 @@
     </x:row>
     <x:row r="269" ht="20" customHeight="1">
       <x:c r="A269" s="7" t="d">
-        <x:v>2026-07-25T12:00:00.000Z</x:v>
+        <x:v>2026-07-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B269" s="2" t="str">
         <x:v>Trail</x:v>
@@ -10085,7 +10085,7 @@
     </x:row>
     <x:row r="270" ht="20" customHeight="1">
       <x:c r="A270" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B270" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -10118,7 +10118,7 @@
     </x:row>
     <x:row r="271" ht="20" customHeight="1">
       <x:c r="A271" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B271" s="2" t="str">
         <x:v>Stride</x:v>
@@ -10151,7 +10151,7 @@
     </x:row>
     <x:row r="272" ht="20" customHeight="1">
       <x:c r="A272" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B272" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -10184,7 +10184,7 @@
     </x:row>
     <x:row r="273" ht="20" customHeight="1">
       <x:c r="A273" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B273" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -10217,7 +10217,7 @@
     </x:row>
     <x:row r="274" ht="20" customHeight="1">
       <x:c r="A274" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B274" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -10250,7 +10250,7 @@
     </x:row>
     <x:row r="275" ht="20" customHeight="1">
       <x:c r="A275" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B275" s="2" t="str">
         <x:v>Muse</x:v>
@@ -10283,7 +10283,7 @@
     </x:row>
     <x:row r="276" ht="20" customHeight="1">
       <x:c r="A276" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B276" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -10316,7 +10316,7 @@
     </x:row>
     <x:row r="277" ht="20" customHeight="1">
       <x:c r="A277" s="7" t="d">
-        <x:v>2026-07-26T12:00:00.000Z</x:v>
+        <x:v>2026-07-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B277" s="2" t="str">
         <x:v>Trail</x:v>
@@ -10349,7 +10349,7 @@
     </x:row>
     <x:row r="278" ht="20" customHeight="1">
       <x:c r="A278" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B278" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -10382,7 +10382,7 @@
     </x:row>
     <x:row r="279" ht="20" customHeight="1">
       <x:c r="A279" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B279" s="2" t="str">
         <x:v>Stride</x:v>
@@ -10415,7 +10415,7 @@
     </x:row>
     <x:row r="280" ht="20" customHeight="1">
       <x:c r="A280" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B280" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -10448,7 +10448,7 @@
     </x:row>
     <x:row r="281" ht="20" customHeight="1">
       <x:c r="A281" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B281" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -10481,7 +10481,7 @@
     </x:row>
     <x:row r="282" ht="20" customHeight="1">
       <x:c r="A282" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B282" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -10514,7 +10514,7 @@
     </x:row>
     <x:row r="283" ht="20" customHeight="1">
       <x:c r="A283" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B283" s="2" t="str">
         <x:v>Muse</x:v>
@@ -10547,7 +10547,7 @@
     </x:row>
     <x:row r="284" ht="20" customHeight="1">
       <x:c r="A284" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B284" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -10580,7 +10580,7 @@
     </x:row>
     <x:row r="285" ht="20" customHeight="1">
       <x:c r="A285" s="7" t="d">
-        <x:v>2026-07-27T12:00:00.000Z</x:v>
+        <x:v>2026-07-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B285" s="2" t="str">
         <x:v>Trail</x:v>
@@ -10613,7 +10613,7 @@
     </x:row>
     <x:row r="286" ht="20" customHeight="1">
       <x:c r="A286" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B286" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -10646,7 +10646,7 @@
     </x:row>
     <x:row r="287" ht="20" customHeight="1">
       <x:c r="A287" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B287" s="2" t="str">
         <x:v>Stride</x:v>
@@ -10679,7 +10679,7 @@
     </x:row>
     <x:row r="288" ht="20" customHeight="1">
       <x:c r="A288" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B288" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -10712,7 +10712,7 @@
     </x:row>
     <x:row r="289" ht="20" customHeight="1">
       <x:c r="A289" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B289" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -10745,7 +10745,7 @@
     </x:row>
     <x:row r="290" ht="20" customHeight="1">
       <x:c r="A290" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B290" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -10778,7 +10778,7 @@
     </x:row>
     <x:row r="291" ht="20" customHeight="1">
       <x:c r="A291" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B291" s="2" t="str">
         <x:v>Muse</x:v>
@@ -10811,7 +10811,7 @@
     </x:row>
     <x:row r="292" ht="20" customHeight="1">
       <x:c r="A292" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B292" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -10844,7 +10844,7 @@
     </x:row>
     <x:row r="293" ht="20" customHeight="1">
       <x:c r="A293" s="7" t="d">
-        <x:v>2026-07-28T12:00:00.000Z</x:v>
+        <x:v>2026-07-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B293" s="2" t="str">
         <x:v>Trail</x:v>
@@ -10877,7 +10877,7 @@
     </x:row>
     <x:row r="294" ht="20" customHeight="1">
       <x:c r="A294" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B294" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -10910,7 +10910,7 @@
     </x:row>
     <x:row r="295" ht="20" customHeight="1">
       <x:c r="A295" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B295" s="2" t="str">
         <x:v>Stride</x:v>
@@ -10943,7 +10943,7 @@
     </x:row>
     <x:row r="296" ht="20" customHeight="1">
       <x:c r="A296" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B296" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -10976,7 +10976,7 @@
     </x:row>
     <x:row r="297" ht="20" customHeight="1">
       <x:c r="A297" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B297" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -11009,7 +11009,7 @@
     </x:row>
     <x:row r="298" ht="20" customHeight="1">
       <x:c r="A298" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B298" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -11042,7 +11042,7 @@
     </x:row>
     <x:row r="299" ht="20" customHeight="1">
       <x:c r="A299" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B299" s="2" t="str">
         <x:v>Muse</x:v>
@@ -11075,7 +11075,7 @@
     </x:row>
     <x:row r="300" ht="20" customHeight="1">
       <x:c r="A300" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B300" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -11108,7 +11108,7 @@
     </x:row>
     <x:row r="301" ht="20" customHeight="1">
       <x:c r="A301" s="7" t="d">
-        <x:v>2026-07-29T12:00:00.000Z</x:v>
+        <x:v>2026-07-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B301" s="2" t="str">
         <x:v>Trail</x:v>
@@ -11141,7 +11141,7 @@
     </x:row>
     <x:row r="302" ht="20" customHeight="1">
       <x:c r="A302" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B302" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -11174,7 +11174,7 @@
     </x:row>
     <x:row r="303" ht="20" customHeight="1">
       <x:c r="A303" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B303" s="2" t="str">
         <x:v>Stride</x:v>
@@ -11207,7 +11207,7 @@
     </x:row>
     <x:row r="304" ht="20" customHeight="1">
       <x:c r="A304" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B304" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -11240,7 +11240,7 @@
     </x:row>
     <x:row r="305" ht="20" customHeight="1">
       <x:c r="A305" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B305" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -11273,7 +11273,7 @@
     </x:row>
     <x:row r="306" ht="20" customHeight="1">
       <x:c r="A306" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B306" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -11306,7 +11306,7 @@
     </x:row>
     <x:row r="307" ht="20" customHeight="1">
       <x:c r="A307" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B307" s="2" t="str">
         <x:v>Muse</x:v>
@@ -11339,7 +11339,7 @@
     </x:row>
     <x:row r="308" ht="20" customHeight="1">
       <x:c r="A308" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B308" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -11372,7 +11372,7 @@
     </x:row>
     <x:row r="309" ht="20" customHeight="1">
       <x:c r="A309" s="7" t="d">
-        <x:v>2026-07-30T12:00:00.000Z</x:v>
+        <x:v>2026-07-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B309" s="2" t="str">
         <x:v>Trail</x:v>
@@ -11405,7 +11405,7 @@
     </x:row>
     <x:row r="310" ht="20" customHeight="1">
       <x:c r="A310" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B310" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -11438,7 +11438,7 @@
     </x:row>
     <x:row r="311" ht="20" customHeight="1">
       <x:c r="A311" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B311" s="2" t="str">
         <x:v>Stride</x:v>
@@ -11471,7 +11471,7 @@
     </x:row>
     <x:row r="312" ht="20" customHeight="1">
       <x:c r="A312" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B312" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -11504,7 +11504,7 @@
     </x:row>
     <x:row r="313" ht="20" customHeight="1">
       <x:c r="A313" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B313" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -11537,7 +11537,7 @@
     </x:row>
     <x:row r="314" ht="20" customHeight="1">
       <x:c r="A314" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B314" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -11570,7 +11570,7 @@
     </x:row>
     <x:row r="315" ht="20" customHeight="1">
       <x:c r="A315" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B315" s="2" t="str">
         <x:v>Muse</x:v>
@@ -11603,7 +11603,7 @@
     </x:row>
     <x:row r="316" ht="20" customHeight="1">
       <x:c r="A316" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B316" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -11636,7 +11636,7 @@
     </x:row>
     <x:row r="317" ht="20" customHeight="1">
       <x:c r="A317" s="7" t="d">
-        <x:v>2026-07-31T12:00:00.000Z</x:v>
+        <x:v>2026-07-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B317" s="2" t="str">
         <x:v>Trail</x:v>
@@ -11669,7 +11669,7 @@
     </x:row>
     <x:row r="318" ht="20" customHeight="1">
       <x:c r="A318" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B318" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -11702,7 +11702,7 @@
     </x:row>
     <x:row r="319" ht="20" customHeight="1">
       <x:c r="A319" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B319" s="2" t="str">
         <x:v>Stride</x:v>
@@ -11735,7 +11735,7 @@
     </x:row>
     <x:row r="320" ht="20" customHeight="1">
       <x:c r="A320" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B320" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -11768,7 +11768,7 @@
     </x:row>
     <x:row r="321" ht="20" customHeight="1">
       <x:c r="A321" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B321" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -11801,7 +11801,7 @@
     </x:row>
     <x:row r="322" ht="20" customHeight="1">
       <x:c r="A322" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B322" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -11834,7 +11834,7 @@
     </x:row>
     <x:row r="323" ht="20" customHeight="1">
       <x:c r="A323" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B323" s="2" t="str">
         <x:v>Muse</x:v>
@@ -11867,7 +11867,7 @@
     </x:row>
     <x:row r="324" ht="20" customHeight="1">
       <x:c r="A324" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B324" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -11900,7 +11900,7 @@
     </x:row>
     <x:row r="325" ht="20" customHeight="1">
       <x:c r="A325" s="7" t="d">
-        <x:v>2026-08-01T12:00:00.000Z</x:v>
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B325" s="2" t="str">
         <x:v>Trail</x:v>
@@ -11933,7 +11933,7 @@
     </x:row>
     <x:row r="326" ht="20" customHeight="1">
       <x:c r="A326" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B326" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -11966,7 +11966,7 @@
     </x:row>
     <x:row r="327" ht="20" customHeight="1">
       <x:c r="A327" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B327" s="2" t="str">
         <x:v>Stride</x:v>
@@ -11999,7 +11999,7 @@
     </x:row>
     <x:row r="328" ht="20" customHeight="1">
       <x:c r="A328" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B328" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -12032,7 +12032,7 @@
     </x:row>
     <x:row r="329" ht="20" customHeight="1">
       <x:c r="A329" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B329" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -12065,7 +12065,7 @@
     </x:row>
     <x:row r="330" ht="20" customHeight="1">
       <x:c r="A330" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B330" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -12098,7 +12098,7 @@
     </x:row>
     <x:row r="331" ht="20" customHeight="1">
       <x:c r="A331" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B331" s="2" t="str">
         <x:v>Muse</x:v>
@@ -12131,7 +12131,7 @@
     </x:row>
     <x:row r="332" ht="20" customHeight="1">
       <x:c r="A332" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B332" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -12164,7 +12164,7 @@
     </x:row>
     <x:row r="333" ht="20" customHeight="1">
       <x:c r="A333" s="7" t="d">
-        <x:v>2026-08-02T12:00:00.000Z</x:v>
+        <x:v>2026-08-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B333" s="2" t="str">
         <x:v>Trail</x:v>
@@ -12197,7 +12197,7 @@
     </x:row>
     <x:row r="334" ht="20" customHeight="1">
       <x:c r="A334" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B334" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -12230,7 +12230,7 @@
     </x:row>
     <x:row r="335" ht="20" customHeight="1">
       <x:c r="A335" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B335" s="2" t="str">
         <x:v>Stride</x:v>
@@ -12263,7 +12263,7 @@
     </x:row>
     <x:row r="336" ht="20" customHeight="1">
       <x:c r="A336" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B336" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -12296,7 +12296,7 @@
     </x:row>
     <x:row r="337" ht="20" customHeight="1">
       <x:c r="A337" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B337" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -12329,7 +12329,7 @@
     </x:row>
     <x:row r="338" ht="20" customHeight="1">
       <x:c r="A338" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B338" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -12362,7 +12362,7 @@
     </x:row>
     <x:row r="339" ht="20" customHeight="1">
       <x:c r="A339" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B339" s="2" t="str">
         <x:v>Muse</x:v>
@@ -12395,7 +12395,7 @@
     </x:row>
     <x:row r="340" ht="20" customHeight="1">
       <x:c r="A340" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B340" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -12428,7 +12428,7 @@
     </x:row>
     <x:row r="341" ht="20" customHeight="1">
       <x:c r="A341" s="7" t="d">
-        <x:v>2026-08-03T12:00:00.000Z</x:v>
+        <x:v>2026-08-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B341" s="2" t="str">
         <x:v>Trail</x:v>
@@ -12461,7 +12461,7 @@
     </x:row>
     <x:row r="342" ht="20" customHeight="1">
       <x:c r="A342" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B342" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -12494,7 +12494,7 @@
     </x:row>
     <x:row r="343" ht="20" customHeight="1">
       <x:c r="A343" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B343" s="2" t="str">
         <x:v>Stride</x:v>
@@ -12527,7 +12527,7 @@
     </x:row>
     <x:row r="344" ht="20" customHeight="1">
       <x:c r="A344" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B344" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -12560,7 +12560,7 @@
     </x:row>
     <x:row r="345" ht="20" customHeight="1">
       <x:c r="A345" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B345" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -12593,7 +12593,7 @@
     </x:row>
     <x:row r="346" ht="20" customHeight="1">
       <x:c r="A346" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B346" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -12626,7 +12626,7 @@
     </x:row>
     <x:row r="347" ht="20" customHeight="1">
       <x:c r="A347" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B347" s="2" t="str">
         <x:v>Muse</x:v>
@@ -12659,7 +12659,7 @@
     </x:row>
     <x:row r="348" ht="20" customHeight="1">
       <x:c r="A348" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B348" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -12692,7 +12692,7 @@
     </x:row>
     <x:row r="349" ht="20" customHeight="1">
       <x:c r="A349" s="7" t="d">
-        <x:v>2026-08-04T12:00:00.000Z</x:v>
+        <x:v>2026-08-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B349" s="2" t="str">
         <x:v>Trail</x:v>
@@ -12725,7 +12725,7 @@
     </x:row>
     <x:row r="350" ht="20" customHeight="1">
       <x:c r="A350" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B350" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -12758,7 +12758,7 @@
     </x:row>
     <x:row r="351" ht="20" customHeight="1">
       <x:c r="A351" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B351" s="2" t="str">
         <x:v>Stride</x:v>
@@ -12791,7 +12791,7 @@
     </x:row>
     <x:row r="352" ht="20" customHeight="1">
       <x:c r="A352" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B352" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -12824,7 +12824,7 @@
     </x:row>
     <x:row r="353" ht="20" customHeight="1">
       <x:c r="A353" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B353" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -12857,7 +12857,7 @@
     </x:row>
     <x:row r="354" ht="20" customHeight="1">
       <x:c r="A354" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B354" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -12890,7 +12890,7 @@
     </x:row>
     <x:row r="355" ht="20" customHeight="1">
       <x:c r="A355" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B355" s="2" t="str">
         <x:v>Muse</x:v>
@@ -12923,7 +12923,7 @@
     </x:row>
     <x:row r="356" ht="20" customHeight="1">
       <x:c r="A356" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B356" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -12956,7 +12956,7 @@
     </x:row>
     <x:row r="357" ht="20" customHeight="1">
       <x:c r="A357" s="7" t="d">
-        <x:v>2026-08-05T12:00:00.000Z</x:v>
+        <x:v>2026-08-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B357" s="2" t="str">
         <x:v>Trail</x:v>
@@ -12989,7 +12989,7 @@
     </x:row>
     <x:row r="358" ht="20" customHeight="1">
       <x:c r="A358" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B358" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -13022,7 +13022,7 @@
     </x:row>
     <x:row r="359" ht="20" customHeight="1">
       <x:c r="A359" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B359" s="2" t="str">
         <x:v>Stride</x:v>
@@ -13055,7 +13055,7 @@
     </x:row>
     <x:row r="360" ht="20" customHeight="1">
       <x:c r="A360" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B360" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -13088,7 +13088,7 @@
     </x:row>
     <x:row r="361" ht="20" customHeight="1">
       <x:c r="A361" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B361" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -13121,7 +13121,7 @@
     </x:row>
     <x:row r="362" ht="20" customHeight="1">
       <x:c r="A362" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B362" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -13154,7 +13154,7 @@
     </x:row>
     <x:row r="363" ht="20" customHeight="1">
       <x:c r="A363" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B363" s="2" t="str">
         <x:v>Muse</x:v>
@@ -13187,7 +13187,7 @@
     </x:row>
     <x:row r="364" ht="20" customHeight="1">
       <x:c r="A364" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B364" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -13220,7 +13220,7 @@
     </x:row>
     <x:row r="365" ht="20" customHeight="1">
       <x:c r="A365" s="7" t="d">
-        <x:v>2026-08-06T12:00:00.000Z</x:v>
+        <x:v>2026-08-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B365" s="2" t="str">
         <x:v>Trail</x:v>
@@ -13253,7 +13253,7 @@
     </x:row>
     <x:row r="366" ht="20" customHeight="1">
       <x:c r="A366" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B366" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -13286,7 +13286,7 @@
     </x:row>
     <x:row r="367" ht="20" customHeight="1">
       <x:c r="A367" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B367" s="2" t="str">
         <x:v>Stride</x:v>
@@ -13319,7 +13319,7 @@
     </x:row>
     <x:row r="368" ht="20" customHeight="1">
       <x:c r="A368" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B368" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -13352,7 +13352,7 @@
     </x:row>
     <x:row r="369" ht="20" customHeight="1">
       <x:c r="A369" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B369" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -13385,7 +13385,7 @@
     </x:row>
     <x:row r="370" ht="20" customHeight="1">
       <x:c r="A370" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B370" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -13418,7 +13418,7 @@
     </x:row>
     <x:row r="371" ht="20" customHeight="1">
       <x:c r="A371" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B371" s="2" t="str">
         <x:v>Muse</x:v>
@@ -13451,7 +13451,7 @@
     </x:row>
     <x:row r="372" ht="20" customHeight="1">
       <x:c r="A372" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B372" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -13484,7 +13484,7 @@
     </x:row>
     <x:row r="373" ht="20" customHeight="1">
       <x:c r="A373" s="7" t="d">
-        <x:v>2026-08-07T12:00:00.000Z</x:v>
+        <x:v>2026-08-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B373" s="2" t="str">
         <x:v>Trail</x:v>
@@ -13517,7 +13517,7 @@
     </x:row>
     <x:row r="374" ht="20" customHeight="1">
       <x:c r="A374" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B374" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -13550,7 +13550,7 @@
     </x:row>
     <x:row r="375" ht="20" customHeight="1">
       <x:c r="A375" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B375" s="2" t="str">
         <x:v>Stride</x:v>
@@ -13583,7 +13583,7 @@
     </x:row>
     <x:row r="376" ht="20" customHeight="1">
       <x:c r="A376" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B376" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -13616,7 +13616,7 @@
     </x:row>
     <x:row r="377" ht="20" customHeight="1">
       <x:c r="A377" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B377" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -13649,7 +13649,7 @@
     </x:row>
     <x:row r="378" ht="20" customHeight="1">
       <x:c r="A378" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B378" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -13682,7 +13682,7 @@
     </x:row>
     <x:row r="379" ht="20" customHeight="1">
       <x:c r="A379" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B379" s="2" t="str">
         <x:v>Muse</x:v>
@@ -13715,7 +13715,7 @@
     </x:row>
     <x:row r="380" ht="20" customHeight="1">
       <x:c r="A380" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B380" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -13748,7 +13748,7 @@
     </x:row>
     <x:row r="381" ht="20" customHeight="1">
       <x:c r="A381" s="7" t="d">
-        <x:v>2026-08-08T12:00:00.000Z</x:v>
+        <x:v>2026-08-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B381" s="2" t="str">
         <x:v>Trail</x:v>
@@ -13781,7 +13781,7 @@
     </x:row>
     <x:row r="382" ht="20" customHeight="1">
       <x:c r="A382" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B382" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -13814,7 +13814,7 @@
     </x:row>
     <x:row r="383" ht="20" customHeight="1">
       <x:c r="A383" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B383" s="2" t="str">
         <x:v>Stride</x:v>
@@ -13847,7 +13847,7 @@
     </x:row>
     <x:row r="384" ht="20" customHeight="1">
       <x:c r="A384" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B384" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -13880,7 +13880,7 @@
     </x:row>
     <x:row r="385" ht="20" customHeight="1">
       <x:c r="A385" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B385" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -13913,7 +13913,7 @@
     </x:row>
     <x:row r="386" ht="20" customHeight="1">
       <x:c r="A386" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B386" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -13946,7 +13946,7 @@
     </x:row>
     <x:row r="387" ht="20" customHeight="1">
       <x:c r="A387" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B387" s="2" t="str">
         <x:v>Muse</x:v>
@@ -13979,7 +13979,7 @@
     </x:row>
     <x:row r="388" ht="20" customHeight="1">
       <x:c r="A388" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B388" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -14012,7 +14012,7 @@
     </x:row>
     <x:row r="389" ht="20" customHeight="1">
       <x:c r="A389" s="7" t="d">
-        <x:v>2026-08-09T12:00:00.000Z</x:v>
+        <x:v>2026-08-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B389" s="2" t="str">
         <x:v>Trail</x:v>
@@ -14045,7 +14045,7 @@
     </x:row>
     <x:row r="390" ht="20" customHeight="1">
       <x:c r="A390" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B390" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -14078,7 +14078,7 @@
     </x:row>
     <x:row r="391" ht="20" customHeight="1">
       <x:c r="A391" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B391" s="2" t="str">
         <x:v>Stride</x:v>
@@ -14111,7 +14111,7 @@
     </x:row>
     <x:row r="392" ht="20" customHeight="1">
       <x:c r="A392" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B392" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -14144,7 +14144,7 @@
     </x:row>
     <x:row r="393" ht="20" customHeight="1">
       <x:c r="A393" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B393" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -14177,7 +14177,7 @@
     </x:row>
     <x:row r="394" ht="20" customHeight="1">
       <x:c r="A394" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B394" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -14210,7 +14210,7 @@
     </x:row>
     <x:row r="395" ht="20" customHeight="1">
       <x:c r="A395" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B395" s="2" t="str">
         <x:v>Muse</x:v>
@@ -14243,7 +14243,7 @@
     </x:row>
     <x:row r="396" ht="20" customHeight="1">
       <x:c r="A396" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B396" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -14276,7 +14276,7 @@
     </x:row>
     <x:row r="397" ht="20" customHeight="1">
       <x:c r="A397" s="7" t="d">
-        <x:v>2026-08-10T12:00:00.000Z</x:v>
+        <x:v>2026-08-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B397" s="2" t="str">
         <x:v>Trail</x:v>
@@ -14309,7 +14309,7 @@
     </x:row>
     <x:row r="398" ht="20" customHeight="1">
       <x:c r="A398" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B398" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -14342,7 +14342,7 @@
     </x:row>
     <x:row r="399" ht="20" customHeight="1">
       <x:c r="A399" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B399" s="2" t="str">
         <x:v>Stride</x:v>
@@ -14375,7 +14375,7 @@
     </x:row>
     <x:row r="400" ht="20" customHeight="1">
       <x:c r="A400" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B400" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -14408,7 +14408,7 @@
     </x:row>
     <x:row r="401" ht="20" customHeight="1">
       <x:c r="A401" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B401" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -14441,7 +14441,7 @@
     </x:row>
     <x:row r="402" ht="20" customHeight="1">
       <x:c r="A402" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B402" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -14474,7 +14474,7 @@
     </x:row>
     <x:row r="403" ht="20" customHeight="1">
       <x:c r="A403" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B403" s="2" t="str">
         <x:v>Muse</x:v>
@@ -14507,7 +14507,7 @@
     </x:row>
     <x:row r="404" ht="20" customHeight="1">
       <x:c r="A404" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B404" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -14540,7 +14540,7 @@
     </x:row>
     <x:row r="405" ht="20" customHeight="1">
       <x:c r="A405" s="7" t="d">
-        <x:v>2026-08-11T12:00:00.000Z</x:v>
+        <x:v>2026-08-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B405" s="2" t="str">
         <x:v>Trail</x:v>
@@ -14573,7 +14573,7 @@
     </x:row>
     <x:row r="406" ht="20" customHeight="1">
       <x:c r="A406" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B406" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -14606,7 +14606,7 @@
     </x:row>
     <x:row r="407" ht="20" customHeight="1">
       <x:c r="A407" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B407" s="2" t="str">
         <x:v>Stride</x:v>
@@ -14639,7 +14639,7 @@
     </x:row>
     <x:row r="408" ht="20" customHeight="1">
       <x:c r="A408" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B408" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -14672,7 +14672,7 @@
     </x:row>
     <x:row r="409" ht="20" customHeight="1">
       <x:c r="A409" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B409" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -14705,7 +14705,7 @@
     </x:row>
     <x:row r="410" ht="20" customHeight="1">
       <x:c r="A410" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B410" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -14738,7 +14738,7 @@
     </x:row>
     <x:row r="411" ht="20" customHeight="1">
       <x:c r="A411" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B411" s="2" t="str">
         <x:v>Muse</x:v>
@@ -14771,7 +14771,7 @@
     </x:row>
     <x:row r="412" ht="20" customHeight="1">
       <x:c r="A412" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B412" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -14804,7 +14804,7 @@
     </x:row>
     <x:row r="413" ht="20" customHeight="1">
       <x:c r="A413" s="7" t="d">
-        <x:v>2026-08-12T12:00:00.000Z</x:v>
+        <x:v>2026-08-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B413" s="2" t="str">
         <x:v>Trail</x:v>
@@ -14837,7 +14837,7 @@
     </x:row>
     <x:row r="414" ht="20" customHeight="1">
       <x:c r="A414" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B414" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -14870,7 +14870,7 @@
     </x:row>
     <x:row r="415" ht="20" customHeight="1">
       <x:c r="A415" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B415" s="2" t="str">
         <x:v>Stride</x:v>
@@ -14903,7 +14903,7 @@
     </x:row>
     <x:row r="416" ht="20" customHeight="1">
       <x:c r="A416" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B416" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -14936,7 +14936,7 @@
     </x:row>
     <x:row r="417" ht="20" customHeight="1">
       <x:c r="A417" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B417" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -14969,7 +14969,7 @@
     </x:row>
     <x:row r="418" ht="20" customHeight="1">
       <x:c r="A418" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B418" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -15002,7 +15002,7 @@
     </x:row>
     <x:row r="419" ht="20" customHeight="1">
       <x:c r="A419" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B419" s="2" t="str">
         <x:v>Muse</x:v>
@@ -15035,7 +15035,7 @@
     </x:row>
     <x:row r="420" ht="20" customHeight="1">
       <x:c r="A420" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B420" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -15068,7 +15068,7 @@
     </x:row>
     <x:row r="421" ht="20" customHeight="1">
       <x:c r="A421" s="7" t="d">
-        <x:v>2026-08-13T12:00:00.000Z</x:v>
+        <x:v>2026-08-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B421" s="2" t="str">
         <x:v>Trail</x:v>
@@ -15101,7 +15101,7 @@
     </x:row>
     <x:row r="422" ht="20" customHeight="1">
       <x:c r="A422" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B422" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -15134,7 +15134,7 @@
     </x:row>
     <x:row r="423" ht="20" customHeight="1">
       <x:c r="A423" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B423" s="2" t="str">
         <x:v>Stride</x:v>
@@ -15167,7 +15167,7 @@
     </x:row>
     <x:row r="424" ht="20" customHeight="1">
       <x:c r="A424" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B424" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -15200,7 +15200,7 @@
     </x:row>
     <x:row r="425" ht="20" customHeight="1">
       <x:c r="A425" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B425" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -15233,7 +15233,7 @@
     </x:row>
     <x:row r="426" ht="20" customHeight="1">
       <x:c r="A426" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B426" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -15266,7 +15266,7 @@
     </x:row>
     <x:row r="427" ht="20" customHeight="1">
       <x:c r="A427" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B427" s="2" t="str">
         <x:v>Muse</x:v>
@@ -15299,7 +15299,7 @@
     </x:row>
     <x:row r="428" ht="20" customHeight="1">
       <x:c r="A428" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B428" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -15332,7 +15332,7 @@
     </x:row>
     <x:row r="429" ht="20" customHeight="1">
       <x:c r="A429" s="7" t="d">
-        <x:v>2026-08-14T12:00:00.000Z</x:v>
+        <x:v>2026-08-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B429" s="2" t="str">
         <x:v>Trail</x:v>
@@ -15365,7 +15365,7 @@
     </x:row>
     <x:row r="430" ht="20" customHeight="1">
       <x:c r="A430" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B430" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -15398,7 +15398,7 @@
     </x:row>
     <x:row r="431" ht="20" customHeight="1">
       <x:c r="A431" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B431" s="2" t="str">
         <x:v>Stride</x:v>
@@ -15431,7 +15431,7 @@
     </x:row>
     <x:row r="432" ht="20" customHeight="1">
       <x:c r="A432" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B432" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -15464,7 +15464,7 @@
     </x:row>
     <x:row r="433" ht="20" customHeight="1">
       <x:c r="A433" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B433" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -15497,7 +15497,7 @@
     </x:row>
     <x:row r="434" ht="20" customHeight="1">
       <x:c r="A434" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B434" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -15530,7 +15530,7 @@
     </x:row>
     <x:row r="435" ht="20" customHeight="1">
       <x:c r="A435" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B435" s="2" t="str">
         <x:v>Muse</x:v>
@@ -15563,7 +15563,7 @@
     </x:row>
     <x:row r="436" ht="20" customHeight="1">
       <x:c r="A436" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B436" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -15596,7 +15596,7 @@
     </x:row>
     <x:row r="437" ht="20" customHeight="1">
       <x:c r="A437" s="7" t="d">
-        <x:v>2026-08-15T12:00:00.000Z</x:v>
+        <x:v>2026-08-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B437" s="2" t="str">
         <x:v>Trail</x:v>
@@ -15629,7 +15629,7 @@
     </x:row>
     <x:row r="438" ht="20" customHeight="1">
       <x:c r="A438" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B438" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -15662,7 +15662,7 @@
     </x:row>
     <x:row r="439" ht="20" customHeight="1">
       <x:c r="A439" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B439" s="2" t="str">
         <x:v>Stride</x:v>
@@ -15695,7 +15695,7 @@
     </x:row>
     <x:row r="440" ht="20" customHeight="1">
       <x:c r="A440" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B440" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -15728,7 +15728,7 @@
     </x:row>
     <x:row r="441" ht="20" customHeight="1">
       <x:c r="A441" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B441" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -15761,7 +15761,7 @@
     </x:row>
     <x:row r="442" ht="20" customHeight="1">
       <x:c r="A442" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B442" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -15794,7 +15794,7 @@
     </x:row>
     <x:row r="443" ht="20" customHeight="1">
       <x:c r="A443" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B443" s="2" t="str">
         <x:v>Muse</x:v>
@@ -15827,7 +15827,7 @@
     </x:row>
     <x:row r="444" ht="20" customHeight="1">
       <x:c r="A444" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B444" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -15860,7 +15860,7 @@
     </x:row>
     <x:row r="445" ht="20" customHeight="1">
       <x:c r="A445" s="7" t="d">
-        <x:v>2026-08-16T12:00:00.000Z</x:v>
+        <x:v>2026-08-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B445" s="2" t="str">
         <x:v>Trail</x:v>
@@ -15893,7 +15893,7 @@
     </x:row>
     <x:row r="446" ht="20" customHeight="1">
       <x:c r="A446" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B446" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -15926,7 +15926,7 @@
     </x:row>
     <x:row r="447" ht="20" customHeight="1">
       <x:c r="A447" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B447" s="2" t="str">
         <x:v>Stride</x:v>
@@ -15959,7 +15959,7 @@
     </x:row>
     <x:row r="448" ht="20" customHeight="1">
       <x:c r="A448" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B448" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -15992,7 +15992,7 @@
     </x:row>
     <x:row r="449" ht="20" customHeight="1">
       <x:c r="A449" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B449" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -16025,7 +16025,7 @@
     </x:row>
     <x:row r="450" ht="20" customHeight="1">
       <x:c r="A450" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B450" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -16058,7 +16058,7 @@
     </x:row>
     <x:row r="451" ht="20" customHeight="1">
       <x:c r="A451" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B451" s="2" t="str">
         <x:v>Muse</x:v>
@@ -16091,7 +16091,7 @@
     </x:row>
     <x:row r="452" ht="20" customHeight="1">
       <x:c r="A452" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B452" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -16124,7 +16124,7 @@
     </x:row>
     <x:row r="453" ht="20" customHeight="1">
       <x:c r="A453" s="7" t="d">
-        <x:v>2026-08-17T12:00:00.000Z</x:v>
+        <x:v>2026-08-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B453" s="2" t="str">
         <x:v>Trail</x:v>
@@ -16157,7 +16157,7 @@
     </x:row>
     <x:row r="454" ht="20" customHeight="1">
       <x:c r="A454" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B454" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -16190,7 +16190,7 @@
     </x:row>
     <x:row r="455" ht="20" customHeight="1">
       <x:c r="A455" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B455" s="2" t="str">
         <x:v>Stride</x:v>
@@ -16223,7 +16223,7 @@
     </x:row>
     <x:row r="456" ht="20" customHeight="1">
       <x:c r="A456" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B456" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -16256,7 +16256,7 @@
     </x:row>
     <x:row r="457" ht="20" customHeight="1">
       <x:c r="A457" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B457" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -16289,7 +16289,7 @@
     </x:row>
     <x:row r="458" ht="20" customHeight="1">
       <x:c r="A458" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B458" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -16322,7 +16322,7 @@
     </x:row>
     <x:row r="459" ht="20" customHeight="1">
       <x:c r="A459" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B459" s="2" t="str">
         <x:v>Muse</x:v>
@@ -16355,7 +16355,7 @@
     </x:row>
     <x:row r="460" ht="20" customHeight="1">
       <x:c r="A460" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B460" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -16388,7 +16388,7 @@
     </x:row>
     <x:row r="461" ht="20" customHeight="1">
       <x:c r="A461" s="7" t="d">
-        <x:v>2026-08-18T12:00:00.000Z</x:v>
+        <x:v>2026-08-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B461" s="2" t="str">
         <x:v>Trail</x:v>
@@ -16421,7 +16421,7 @@
     </x:row>
     <x:row r="462" ht="20" customHeight="1">
       <x:c r="A462" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B462" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -16454,7 +16454,7 @@
     </x:row>
     <x:row r="463" ht="20" customHeight="1">
       <x:c r="A463" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B463" s="2" t="str">
         <x:v>Stride</x:v>
@@ -16487,7 +16487,7 @@
     </x:row>
     <x:row r="464" ht="20" customHeight="1">
       <x:c r="A464" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B464" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -16520,7 +16520,7 @@
     </x:row>
     <x:row r="465" ht="20" customHeight="1">
       <x:c r="A465" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B465" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -16553,7 +16553,7 @@
     </x:row>
     <x:row r="466" ht="20" customHeight="1">
       <x:c r="A466" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B466" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -16586,7 +16586,7 @@
     </x:row>
     <x:row r="467" ht="20" customHeight="1">
       <x:c r="A467" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B467" s="2" t="str">
         <x:v>Muse</x:v>
@@ -16619,7 +16619,7 @@
     </x:row>
     <x:row r="468" ht="20" customHeight="1">
       <x:c r="A468" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B468" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -16652,7 +16652,7 @@
     </x:row>
     <x:row r="469" ht="20" customHeight="1">
       <x:c r="A469" s="7" t="d">
-        <x:v>2026-08-19T12:00:00.000Z</x:v>
+        <x:v>2026-08-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B469" s="2" t="str">
         <x:v>Trail</x:v>
@@ -16685,7 +16685,7 @@
     </x:row>
     <x:row r="470" ht="20" customHeight="1">
       <x:c r="A470" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B470" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -16718,7 +16718,7 @@
     </x:row>
     <x:row r="471" ht="20" customHeight="1">
       <x:c r="A471" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B471" s="2" t="str">
         <x:v>Stride</x:v>
@@ -16751,7 +16751,7 @@
     </x:row>
     <x:row r="472" ht="20" customHeight="1">
       <x:c r="A472" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B472" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -16784,7 +16784,7 @@
     </x:row>
     <x:row r="473" ht="20" customHeight="1">
       <x:c r="A473" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B473" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -16817,7 +16817,7 @@
     </x:row>
     <x:row r="474" ht="20" customHeight="1">
       <x:c r="A474" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B474" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -16850,7 +16850,7 @@
     </x:row>
     <x:row r="475" ht="20" customHeight="1">
       <x:c r="A475" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B475" s="2" t="str">
         <x:v>Muse</x:v>
@@ -16883,7 +16883,7 @@
     </x:row>
     <x:row r="476" ht="20" customHeight="1">
       <x:c r="A476" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B476" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -16916,7 +16916,7 @@
     </x:row>
     <x:row r="477" ht="20" customHeight="1">
       <x:c r="A477" s="7" t="d">
-        <x:v>2026-08-20T12:00:00.000Z</x:v>
+        <x:v>2026-08-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B477" s="2" t="str">
         <x:v>Trail</x:v>
@@ -16949,7 +16949,7 @@
     </x:row>
     <x:row r="478" ht="20" customHeight="1">
       <x:c r="A478" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B478" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -16982,7 +16982,7 @@
     </x:row>
     <x:row r="479" ht="20" customHeight="1">
       <x:c r="A479" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B479" s="2" t="str">
         <x:v>Stride</x:v>
@@ -17015,7 +17015,7 @@
     </x:row>
     <x:row r="480" ht="20" customHeight="1">
       <x:c r="A480" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B480" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -17048,7 +17048,7 @@
     </x:row>
     <x:row r="481" ht="20" customHeight="1">
       <x:c r="A481" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B481" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -17081,7 +17081,7 @@
     </x:row>
     <x:row r="482" ht="20" customHeight="1">
       <x:c r="A482" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B482" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -17114,7 +17114,7 @@
     </x:row>
     <x:row r="483" ht="20" customHeight="1">
       <x:c r="A483" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B483" s="2" t="str">
         <x:v>Muse</x:v>
@@ -17147,7 +17147,7 @@
     </x:row>
     <x:row r="484" ht="20" customHeight="1">
       <x:c r="A484" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B484" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -17180,7 +17180,7 @@
     </x:row>
     <x:row r="485" ht="20" customHeight="1">
       <x:c r="A485" s="7" t="d">
-        <x:v>2026-08-21T12:00:00.000Z</x:v>
+        <x:v>2026-08-21T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B485" s="2" t="str">
         <x:v>Trail</x:v>
@@ -17213,7 +17213,7 @@
     </x:row>
     <x:row r="486" ht="20" customHeight="1">
       <x:c r="A486" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B486" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -17246,7 +17246,7 @@
     </x:row>
     <x:row r="487" ht="20" customHeight="1">
       <x:c r="A487" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B487" s="2" t="str">
         <x:v>Stride</x:v>
@@ -17279,7 +17279,7 @@
     </x:row>
     <x:row r="488" ht="20" customHeight="1">
       <x:c r="A488" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B488" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -17312,7 +17312,7 @@
     </x:row>
     <x:row r="489" ht="20" customHeight="1">
       <x:c r="A489" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B489" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -17345,7 +17345,7 @@
     </x:row>
     <x:row r="490" ht="20" customHeight="1">
       <x:c r="A490" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B490" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -17378,7 +17378,7 @@
     </x:row>
     <x:row r="491" ht="20" customHeight="1">
       <x:c r="A491" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B491" s="2" t="str">
         <x:v>Muse</x:v>
@@ -17411,7 +17411,7 @@
     </x:row>
     <x:row r="492" ht="20" customHeight="1">
       <x:c r="A492" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B492" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -17444,7 +17444,7 @@
     </x:row>
     <x:row r="493" ht="20" customHeight="1">
       <x:c r="A493" s="7" t="d">
-        <x:v>2026-08-22T12:00:00.000Z</x:v>
+        <x:v>2026-08-22T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B493" s="2" t="str">
         <x:v>Trail</x:v>
@@ -17477,7 +17477,7 @@
     </x:row>
     <x:row r="494" ht="20" customHeight="1">
       <x:c r="A494" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B494" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -17510,7 +17510,7 @@
     </x:row>
     <x:row r="495" ht="20" customHeight="1">
       <x:c r="A495" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B495" s="2" t="str">
         <x:v>Stride</x:v>
@@ -17543,7 +17543,7 @@
     </x:row>
     <x:row r="496" ht="20" customHeight="1">
       <x:c r="A496" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B496" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -17576,7 +17576,7 @@
     </x:row>
     <x:row r="497" ht="20" customHeight="1">
       <x:c r="A497" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B497" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -17609,7 +17609,7 @@
     </x:row>
     <x:row r="498" ht="20" customHeight="1">
       <x:c r="A498" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B498" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -17642,7 +17642,7 @@
     </x:row>
     <x:row r="499" ht="20" customHeight="1">
       <x:c r="A499" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B499" s="2" t="str">
         <x:v>Muse</x:v>
@@ -17675,7 +17675,7 @@
     </x:row>
     <x:row r="500" ht="20" customHeight="1">
       <x:c r="A500" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B500" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -17708,7 +17708,7 @@
     </x:row>
     <x:row r="501" ht="20" customHeight="1">
       <x:c r="A501" s="7" t="d">
-        <x:v>2026-08-23T12:00:00.000Z</x:v>
+        <x:v>2026-08-23T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B501" s="2" t="str">
         <x:v>Trail</x:v>
@@ -17741,7 +17741,7 @@
     </x:row>
     <x:row r="502" ht="20" customHeight="1">
       <x:c r="A502" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B502" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -17774,7 +17774,7 @@
     </x:row>
     <x:row r="503" ht="20" customHeight="1">
       <x:c r="A503" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B503" s="2" t="str">
         <x:v>Stride</x:v>
@@ -17807,7 +17807,7 @@
     </x:row>
     <x:row r="504" ht="20" customHeight="1">
       <x:c r="A504" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B504" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -17840,7 +17840,7 @@
     </x:row>
     <x:row r="505" ht="20" customHeight="1">
       <x:c r="A505" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B505" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -17873,7 +17873,7 @@
     </x:row>
     <x:row r="506" ht="20" customHeight="1">
       <x:c r="A506" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B506" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -17906,7 +17906,7 @@
     </x:row>
     <x:row r="507" ht="20" customHeight="1">
       <x:c r="A507" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B507" s="2" t="str">
         <x:v>Muse</x:v>
@@ -17939,7 +17939,7 @@
     </x:row>
     <x:row r="508" ht="20" customHeight="1">
       <x:c r="A508" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B508" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -17972,7 +17972,7 @@
     </x:row>
     <x:row r="509" ht="20" customHeight="1">
       <x:c r="A509" s="7" t="d">
-        <x:v>2026-08-24T12:00:00.000Z</x:v>
+        <x:v>2026-08-24T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B509" s="2" t="str">
         <x:v>Trail</x:v>
@@ -18005,7 +18005,7 @@
     </x:row>
     <x:row r="510" ht="20" customHeight="1">
       <x:c r="A510" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B510" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -18038,7 +18038,7 @@
     </x:row>
     <x:row r="511" ht="20" customHeight="1">
       <x:c r="A511" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B511" s="2" t="str">
         <x:v>Stride</x:v>
@@ -18071,7 +18071,7 @@
     </x:row>
     <x:row r="512" ht="20" customHeight="1">
       <x:c r="A512" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B512" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -18104,7 +18104,7 @@
     </x:row>
     <x:row r="513" ht="20" customHeight="1">
       <x:c r="A513" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B513" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -18137,7 +18137,7 @@
     </x:row>
     <x:row r="514" ht="20" customHeight="1">
       <x:c r="A514" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B514" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -18170,7 +18170,7 @@
     </x:row>
     <x:row r="515" ht="20" customHeight="1">
       <x:c r="A515" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B515" s="2" t="str">
         <x:v>Muse</x:v>
@@ -18203,7 +18203,7 @@
     </x:row>
     <x:row r="516" ht="20" customHeight="1">
       <x:c r="A516" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B516" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -18236,7 +18236,7 @@
     </x:row>
     <x:row r="517" ht="20" customHeight="1">
       <x:c r="A517" s="7" t="d">
-        <x:v>2026-08-25T12:00:00.000Z</x:v>
+        <x:v>2026-08-25T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B517" s="2" t="str">
         <x:v>Trail</x:v>
@@ -18269,7 +18269,7 @@
     </x:row>
     <x:row r="518" ht="20" customHeight="1">
       <x:c r="A518" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B518" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -18302,7 +18302,7 @@
     </x:row>
     <x:row r="519" ht="20" customHeight="1">
       <x:c r="A519" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B519" s="2" t="str">
         <x:v>Stride</x:v>
@@ -18335,7 +18335,7 @@
     </x:row>
     <x:row r="520" ht="20" customHeight="1">
       <x:c r="A520" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B520" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -18368,7 +18368,7 @@
     </x:row>
     <x:row r="521" ht="20" customHeight="1">
       <x:c r="A521" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B521" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -18401,7 +18401,7 @@
     </x:row>
     <x:row r="522" ht="20" customHeight="1">
       <x:c r="A522" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B522" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -18434,7 +18434,7 @@
     </x:row>
     <x:row r="523" ht="20" customHeight="1">
       <x:c r="A523" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B523" s="2" t="str">
         <x:v>Muse</x:v>
@@ -18467,7 +18467,7 @@
     </x:row>
     <x:row r="524" ht="20" customHeight="1">
       <x:c r="A524" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B524" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -18500,7 +18500,7 @@
     </x:row>
     <x:row r="525" ht="20" customHeight="1">
       <x:c r="A525" s="7" t="d">
-        <x:v>2026-08-26T12:00:00.000Z</x:v>
+        <x:v>2026-08-26T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B525" s="2" t="str">
         <x:v>Trail</x:v>
@@ -18533,7 +18533,7 @@
     </x:row>
     <x:row r="526" ht="20" customHeight="1">
       <x:c r="A526" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B526" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -18566,7 +18566,7 @@
     </x:row>
     <x:row r="527" ht="20" customHeight="1">
       <x:c r="A527" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B527" s="2" t="str">
         <x:v>Stride</x:v>
@@ -18599,7 +18599,7 @@
     </x:row>
     <x:row r="528" ht="20" customHeight="1">
       <x:c r="A528" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B528" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -18632,7 +18632,7 @@
     </x:row>
     <x:row r="529" ht="20" customHeight="1">
       <x:c r="A529" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B529" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -18665,7 +18665,7 @@
     </x:row>
     <x:row r="530" ht="20" customHeight="1">
       <x:c r="A530" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B530" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -18698,7 +18698,7 @@
     </x:row>
     <x:row r="531" ht="20" customHeight="1">
       <x:c r="A531" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B531" s="2" t="str">
         <x:v>Muse</x:v>
@@ -18731,7 +18731,7 @@
     </x:row>
     <x:row r="532" ht="20" customHeight="1">
       <x:c r="A532" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B532" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -18764,7 +18764,7 @@
     </x:row>
     <x:row r="533" ht="20" customHeight="1">
       <x:c r="A533" s="7" t="d">
-        <x:v>2026-08-27T12:00:00.000Z</x:v>
+        <x:v>2026-08-27T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B533" s="2" t="str">
         <x:v>Trail</x:v>
@@ -18797,7 +18797,7 @@
     </x:row>
     <x:row r="534" ht="20" customHeight="1">
       <x:c r="A534" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B534" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -18830,7 +18830,7 @@
     </x:row>
     <x:row r="535" ht="20" customHeight="1">
       <x:c r="A535" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B535" s="2" t="str">
         <x:v>Stride</x:v>
@@ -18863,7 +18863,7 @@
     </x:row>
     <x:row r="536" ht="20" customHeight="1">
       <x:c r="A536" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B536" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -18896,7 +18896,7 @@
     </x:row>
     <x:row r="537" ht="20" customHeight="1">
       <x:c r="A537" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B537" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -18929,7 +18929,7 @@
     </x:row>
     <x:row r="538" ht="20" customHeight="1">
       <x:c r="A538" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B538" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -18962,7 +18962,7 @@
     </x:row>
     <x:row r="539" ht="20" customHeight="1">
       <x:c r="A539" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B539" s="2" t="str">
         <x:v>Muse</x:v>
@@ -18995,7 +18995,7 @@
     </x:row>
     <x:row r="540" ht="20" customHeight="1">
       <x:c r="A540" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B540" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -19028,7 +19028,7 @@
     </x:row>
     <x:row r="541" ht="20" customHeight="1">
       <x:c r="A541" s="7" t="d">
-        <x:v>2026-08-28T12:00:00.000Z</x:v>
+        <x:v>2026-08-28T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B541" s="2" t="str">
         <x:v>Trail</x:v>
@@ -19061,7 +19061,7 @@
     </x:row>
     <x:row r="542" ht="20" customHeight="1">
       <x:c r="A542" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B542" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -19094,7 +19094,7 @@
     </x:row>
     <x:row r="543" ht="20" customHeight="1">
       <x:c r="A543" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B543" s="2" t="str">
         <x:v>Stride</x:v>
@@ -19127,7 +19127,7 @@
     </x:row>
     <x:row r="544" ht="20" customHeight="1">
       <x:c r="A544" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B544" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -19160,7 +19160,7 @@
     </x:row>
     <x:row r="545" ht="20" customHeight="1">
       <x:c r="A545" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B545" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -19193,7 +19193,7 @@
     </x:row>
     <x:row r="546" ht="20" customHeight="1">
       <x:c r="A546" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B546" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -19226,7 +19226,7 @@
     </x:row>
     <x:row r="547" ht="20" customHeight="1">
       <x:c r="A547" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B547" s="2" t="str">
         <x:v>Muse</x:v>
@@ -19259,7 +19259,7 @@
     </x:row>
     <x:row r="548" ht="20" customHeight="1">
       <x:c r="A548" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B548" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -19292,7 +19292,7 @@
     </x:row>
     <x:row r="549" ht="20" customHeight="1">
       <x:c r="A549" s="7" t="d">
-        <x:v>2026-08-29T12:00:00.000Z</x:v>
+        <x:v>2026-08-29T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B549" s="2" t="str">
         <x:v>Trail</x:v>
@@ -19325,7 +19325,7 @@
     </x:row>
     <x:row r="550" ht="20" customHeight="1">
       <x:c r="A550" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B550" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -19358,7 +19358,7 @@
     </x:row>
     <x:row r="551" ht="20" customHeight="1">
       <x:c r="A551" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B551" s="2" t="str">
         <x:v>Stride</x:v>
@@ -19391,7 +19391,7 @@
     </x:row>
     <x:row r="552" ht="20" customHeight="1">
       <x:c r="A552" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B552" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -19424,7 +19424,7 @@
     </x:row>
     <x:row r="553" ht="20" customHeight="1">
       <x:c r="A553" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B553" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -19457,7 +19457,7 @@
     </x:row>
     <x:row r="554" ht="20" customHeight="1">
       <x:c r="A554" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B554" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -19490,7 +19490,7 @@
     </x:row>
     <x:row r="555" ht="20" customHeight="1">
       <x:c r="A555" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B555" s="2" t="str">
         <x:v>Muse</x:v>
@@ -19523,7 +19523,7 @@
     </x:row>
     <x:row r="556" ht="20" customHeight="1">
       <x:c r="A556" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B556" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -19556,7 +19556,7 @@
     </x:row>
     <x:row r="557" ht="20" customHeight="1">
       <x:c r="A557" s="7" t="d">
-        <x:v>2026-08-30T12:00:00.000Z</x:v>
+        <x:v>2026-08-30T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B557" s="2" t="str">
         <x:v>Trail</x:v>
@@ -19589,7 +19589,7 @@
     </x:row>
     <x:row r="558" ht="20" customHeight="1">
       <x:c r="A558" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B558" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -19622,7 +19622,7 @@
     </x:row>
     <x:row r="559" ht="20" customHeight="1">
       <x:c r="A559" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B559" s="2" t="str">
         <x:v>Stride</x:v>
@@ -19655,7 +19655,7 @@
     </x:row>
     <x:row r="560" ht="20" customHeight="1">
       <x:c r="A560" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B560" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -19688,7 +19688,7 @@
     </x:row>
     <x:row r="561" ht="20" customHeight="1">
       <x:c r="A561" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B561" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -19721,7 +19721,7 @@
     </x:row>
     <x:row r="562" ht="20" customHeight="1">
       <x:c r="A562" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B562" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -19754,7 +19754,7 @@
     </x:row>
     <x:row r="563" ht="20" customHeight="1">
       <x:c r="A563" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B563" s="2" t="str">
         <x:v>Muse</x:v>
@@ -19787,7 +19787,7 @@
     </x:row>
     <x:row r="564" ht="20" customHeight="1">
       <x:c r="A564" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B564" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -19820,7 +19820,7 @@
     </x:row>
     <x:row r="565" ht="20" customHeight="1">
       <x:c r="A565" s="7" t="d">
-        <x:v>2026-08-31T12:00:00.000Z</x:v>
+        <x:v>2026-08-31T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B565" s="2" t="str">
         <x:v>Trail</x:v>
@@ -19853,7 +19853,7 @@
     </x:row>
     <x:row r="566" ht="20" customHeight="1">
       <x:c r="A566" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B566" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -19886,7 +19886,7 @@
     </x:row>
     <x:row r="567" ht="20" customHeight="1">
       <x:c r="A567" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B567" s="2" t="str">
         <x:v>Stride</x:v>
@@ -19919,7 +19919,7 @@
     </x:row>
     <x:row r="568" ht="20" customHeight="1">
       <x:c r="A568" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B568" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -19952,7 +19952,7 @@
     </x:row>
     <x:row r="569" ht="20" customHeight="1">
       <x:c r="A569" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B569" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -19985,7 +19985,7 @@
     </x:row>
     <x:row r="570" ht="20" customHeight="1">
       <x:c r="A570" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B570" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -20018,7 +20018,7 @@
     </x:row>
     <x:row r="571" ht="20" customHeight="1">
       <x:c r="A571" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B571" s="2" t="str">
         <x:v>Muse</x:v>
@@ -20051,7 +20051,7 @@
     </x:row>
     <x:row r="572" ht="20" customHeight="1">
       <x:c r="A572" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B572" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -20084,7 +20084,7 @@
     </x:row>
     <x:row r="573" ht="20" customHeight="1">
       <x:c r="A573" s="7" t="d">
-        <x:v>2026-09-01T12:00:00.000Z</x:v>
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B573" s="2" t="str">
         <x:v>Trail</x:v>
@@ -20117,7 +20117,7 @@
     </x:row>
     <x:row r="574" ht="20" customHeight="1">
       <x:c r="A574" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B574" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -20150,7 +20150,7 @@
     </x:row>
     <x:row r="575" ht="20" customHeight="1">
       <x:c r="A575" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B575" s="2" t="str">
         <x:v>Stride</x:v>
@@ -20183,7 +20183,7 @@
     </x:row>
     <x:row r="576" ht="20" customHeight="1">
       <x:c r="A576" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B576" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -20216,7 +20216,7 @@
     </x:row>
     <x:row r="577" ht="20" customHeight="1">
       <x:c r="A577" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B577" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -20249,7 +20249,7 @@
     </x:row>
     <x:row r="578" ht="20" customHeight="1">
       <x:c r="A578" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B578" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -20282,7 +20282,7 @@
     </x:row>
     <x:row r="579" ht="20" customHeight="1">
       <x:c r="A579" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B579" s="2" t="str">
         <x:v>Muse</x:v>
@@ -20315,7 +20315,7 @@
     </x:row>
     <x:row r="580" ht="20" customHeight="1">
       <x:c r="A580" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B580" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -20348,7 +20348,7 @@
     </x:row>
     <x:row r="581" ht="20" customHeight="1">
       <x:c r="A581" s="7" t="d">
-        <x:v>2026-09-02T12:00:00.000Z</x:v>
+        <x:v>2026-09-02T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B581" s="2" t="str">
         <x:v>Trail</x:v>
@@ -20381,7 +20381,7 @@
     </x:row>
     <x:row r="582" ht="20" customHeight="1">
       <x:c r="A582" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B582" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -20414,7 +20414,7 @@
     </x:row>
     <x:row r="583" ht="20" customHeight="1">
       <x:c r="A583" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B583" s="2" t="str">
         <x:v>Stride</x:v>
@@ -20447,7 +20447,7 @@
     </x:row>
     <x:row r="584" ht="20" customHeight="1">
       <x:c r="A584" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B584" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -20480,7 +20480,7 @@
     </x:row>
     <x:row r="585" ht="20" customHeight="1">
       <x:c r="A585" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B585" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -20513,7 +20513,7 @@
     </x:row>
     <x:row r="586" ht="20" customHeight="1">
       <x:c r="A586" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B586" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -20546,7 +20546,7 @@
     </x:row>
     <x:row r="587" ht="20" customHeight="1">
       <x:c r="A587" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B587" s="2" t="str">
         <x:v>Muse</x:v>
@@ -20579,7 +20579,7 @@
     </x:row>
     <x:row r="588" ht="20" customHeight="1">
       <x:c r="A588" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B588" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -20612,7 +20612,7 @@
     </x:row>
     <x:row r="589" ht="20" customHeight="1">
       <x:c r="A589" s="7" t="d">
-        <x:v>2026-09-03T12:00:00.000Z</x:v>
+        <x:v>2026-09-03T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B589" s="2" t="str">
         <x:v>Trail</x:v>
@@ -20645,7 +20645,7 @@
     </x:row>
     <x:row r="590" ht="20" customHeight="1">
       <x:c r="A590" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B590" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -20678,7 +20678,7 @@
     </x:row>
     <x:row r="591" ht="20" customHeight="1">
       <x:c r="A591" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B591" s="2" t="str">
         <x:v>Stride</x:v>
@@ -20711,7 +20711,7 @@
     </x:row>
     <x:row r="592" ht="20" customHeight="1">
       <x:c r="A592" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B592" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -20744,7 +20744,7 @@
     </x:row>
     <x:row r="593" ht="20" customHeight="1">
       <x:c r="A593" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B593" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -20777,7 +20777,7 @@
     </x:row>
     <x:row r="594" ht="20" customHeight="1">
       <x:c r="A594" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B594" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -20810,7 +20810,7 @@
     </x:row>
     <x:row r="595" ht="20" customHeight="1">
       <x:c r="A595" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B595" s="2" t="str">
         <x:v>Muse</x:v>
@@ -20843,7 +20843,7 @@
     </x:row>
     <x:row r="596" ht="20" customHeight="1">
       <x:c r="A596" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B596" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -20876,7 +20876,7 @@
     </x:row>
     <x:row r="597" ht="20" customHeight="1">
       <x:c r="A597" s="7" t="d">
-        <x:v>2026-09-04T12:00:00.000Z</x:v>
+        <x:v>2026-09-04T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B597" s="2" t="str">
         <x:v>Trail</x:v>
@@ -20909,7 +20909,7 @@
     </x:row>
     <x:row r="598" ht="20" customHeight="1">
       <x:c r="A598" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B598" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -20942,7 +20942,7 @@
     </x:row>
     <x:row r="599" ht="20" customHeight="1">
       <x:c r="A599" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B599" s="2" t="str">
         <x:v>Stride</x:v>
@@ -20975,7 +20975,7 @@
     </x:row>
     <x:row r="600" ht="20" customHeight="1">
       <x:c r="A600" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B600" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -21008,7 +21008,7 @@
     </x:row>
     <x:row r="601" ht="20" customHeight="1">
       <x:c r="A601" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B601" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -21041,7 +21041,7 @@
     </x:row>
     <x:row r="602" ht="20" customHeight="1">
       <x:c r="A602" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B602" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -21074,7 +21074,7 @@
     </x:row>
     <x:row r="603" ht="20" customHeight="1">
       <x:c r="A603" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B603" s="2" t="str">
         <x:v>Muse</x:v>
@@ -21107,7 +21107,7 @@
     </x:row>
     <x:row r="604" ht="20" customHeight="1">
       <x:c r="A604" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B604" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -21140,7 +21140,7 @@
     </x:row>
     <x:row r="605" ht="20" customHeight="1">
       <x:c r="A605" s="7" t="d">
-        <x:v>2026-09-05T12:00:00.000Z</x:v>
+        <x:v>2026-09-05T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B605" s="2" t="str">
         <x:v>Trail</x:v>
@@ -21173,7 +21173,7 @@
     </x:row>
     <x:row r="606" ht="20" customHeight="1">
       <x:c r="A606" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B606" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -21206,7 +21206,7 @@
     </x:row>
     <x:row r="607" ht="20" customHeight="1">
       <x:c r="A607" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B607" s="2" t="str">
         <x:v>Stride</x:v>
@@ -21239,7 +21239,7 @@
     </x:row>
     <x:row r="608" ht="20" customHeight="1">
       <x:c r="A608" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B608" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -21272,7 +21272,7 @@
     </x:row>
     <x:row r="609" ht="20" customHeight="1">
       <x:c r="A609" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B609" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -21305,7 +21305,7 @@
     </x:row>
     <x:row r="610" ht="20" customHeight="1">
       <x:c r="A610" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B610" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -21338,7 +21338,7 @@
     </x:row>
     <x:row r="611" ht="20" customHeight="1">
       <x:c r="A611" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B611" s="2" t="str">
         <x:v>Muse</x:v>
@@ -21371,7 +21371,7 @@
     </x:row>
     <x:row r="612" ht="20" customHeight="1">
       <x:c r="A612" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B612" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -21404,7 +21404,7 @@
     </x:row>
     <x:row r="613" ht="20" customHeight="1">
       <x:c r="A613" s="7" t="d">
-        <x:v>2026-09-06T12:00:00.000Z</x:v>
+        <x:v>2026-09-06T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B613" s="2" t="str">
         <x:v>Trail</x:v>
@@ -21437,7 +21437,7 @@
     </x:row>
     <x:row r="614" ht="20" customHeight="1">
       <x:c r="A614" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B614" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -21470,7 +21470,7 @@
     </x:row>
     <x:row r="615" ht="20" customHeight="1">
       <x:c r="A615" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B615" s="2" t="str">
         <x:v>Stride</x:v>
@@ -21503,7 +21503,7 @@
     </x:row>
     <x:row r="616" ht="20" customHeight="1">
       <x:c r="A616" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B616" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -21536,7 +21536,7 @@
     </x:row>
     <x:row r="617" ht="20" customHeight="1">
       <x:c r="A617" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B617" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -21569,7 +21569,7 @@
     </x:row>
     <x:row r="618" ht="20" customHeight="1">
       <x:c r="A618" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B618" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -21602,7 +21602,7 @@
     </x:row>
     <x:row r="619" ht="20" customHeight="1">
       <x:c r="A619" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B619" s="2" t="str">
         <x:v>Muse</x:v>
@@ -21635,7 +21635,7 @@
     </x:row>
     <x:row r="620" ht="20" customHeight="1">
       <x:c r="A620" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B620" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -21668,7 +21668,7 @@
     </x:row>
     <x:row r="621" ht="20" customHeight="1">
       <x:c r="A621" s="7" t="d">
-        <x:v>2026-09-07T12:00:00.000Z</x:v>
+        <x:v>2026-09-07T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B621" s="2" t="str">
         <x:v>Trail</x:v>
@@ -21701,7 +21701,7 @@
     </x:row>
     <x:row r="622" ht="20" customHeight="1">
       <x:c r="A622" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B622" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -21734,7 +21734,7 @@
     </x:row>
     <x:row r="623" ht="20" customHeight="1">
       <x:c r="A623" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B623" s="2" t="str">
         <x:v>Stride</x:v>
@@ -21767,7 +21767,7 @@
     </x:row>
     <x:row r="624" ht="20" customHeight="1">
       <x:c r="A624" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B624" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -21800,7 +21800,7 @@
     </x:row>
     <x:row r="625" ht="20" customHeight="1">
       <x:c r="A625" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B625" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -21833,7 +21833,7 @@
     </x:row>
     <x:row r="626" ht="20" customHeight="1">
       <x:c r="A626" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B626" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -21866,7 +21866,7 @@
     </x:row>
     <x:row r="627" ht="20" customHeight="1">
       <x:c r="A627" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B627" s="2" t="str">
         <x:v>Muse</x:v>
@@ -21899,7 +21899,7 @@
     </x:row>
     <x:row r="628" ht="20" customHeight="1">
       <x:c r="A628" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B628" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -21932,7 +21932,7 @@
     </x:row>
     <x:row r="629" ht="20" customHeight="1">
       <x:c r="A629" s="7" t="d">
-        <x:v>2026-09-08T12:00:00.000Z</x:v>
+        <x:v>2026-09-08T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B629" s="2" t="str">
         <x:v>Trail</x:v>
@@ -21965,7 +21965,7 @@
     </x:row>
     <x:row r="630" ht="20" customHeight="1">
       <x:c r="A630" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B630" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -21998,7 +21998,7 @@
     </x:row>
     <x:row r="631" ht="20" customHeight="1">
       <x:c r="A631" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B631" s="2" t="str">
         <x:v>Stride</x:v>
@@ -22031,7 +22031,7 @@
     </x:row>
     <x:row r="632" ht="20" customHeight="1">
       <x:c r="A632" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B632" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -22064,7 +22064,7 @@
     </x:row>
     <x:row r="633" ht="20" customHeight="1">
       <x:c r="A633" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B633" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -22097,7 +22097,7 @@
     </x:row>
     <x:row r="634" ht="20" customHeight="1">
       <x:c r="A634" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B634" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -22130,7 +22130,7 @@
     </x:row>
     <x:row r="635" ht="20" customHeight="1">
       <x:c r="A635" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B635" s="2" t="str">
         <x:v>Muse</x:v>
@@ -22163,7 +22163,7 @@
     </x:row>
     <x:row r="636" ht="20" customHeight="1">
       <x:c r="A636" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B636" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -22196,7 +22196,7 @@
     </x:row>
     <x:row r="637" ht="20" customHeight="1">
       <x:c r="A637" s="7" t="d">
-        <x:v>2026-09-09T12:00:00.000Z</x:v>
+        <x:v>2026-09-09T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B637" s="2" t="str">
         <x:v>Trail</x:v>
@@ -22229,7 +22229,7 @@
     </x:row>
     <x:row r="638" ht="20" customHeight="1">
       <x:c r="A638" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B638" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -22262,7 +22262,7 @@
     </x:row>
     <x:row r="639" ht="20" customHeight="1">
       <x:c r="A639" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B639" s="2" t="str">
         <x:v>Stride</x:v>
@@ -22295,7 +22295,7 @@
     </x:row>
     <x:row r="640" ht="20" customHeight="1">
       <x:c r="A640" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B640" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -22328,7 +22328,7 @@
     </x:row>
     <x:row r="641" ht="20" customHeight="1">
       <x:c r="A641" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B641" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -22361,7 +22361,7 @@
     </x:row>
     <x:row r="642" ht="20" customHeight="1">
       <x:c r="A642" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B642" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -22394,7 +22394,7 @@
     </x:row>
     <x:row r="643" ht="20" customHeight="1">
       <x:c r="A643" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B643" s="2" t="str">
         <x:v>Muse</x:v>
@@ -22427,7 +22427,7 @@
     </x:row>
     <x:row r="644" ht="20" customHeight="1">
       <x:c r="A644" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B644" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -22460,7 +22460,7 @@
     </x:row>
     <x:row r="645" ht="20" customHeight="1">
       <x:c r="A645" s="7" t="d">
-        <x:v>2026-09-10T12:00:00.000Z</x:v>
+        <x:v>2026-09-10T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B645" s="2" t="str">
         <x:v>Trail</x:v>
@@ -22493,7 +22493,7 @@
     </x:row>
     <x:row r="646" ht="20" customHeight="1">
       <x:c r="A646" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B646" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -22526,7 +22526,7 @@
     </x:row>
     <x:row r="647" ht="20" customHeight="1">
       <x:c r="A647" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B647" s="2" t="str">
         <x:v>Stride</x:v>
@@ -22559,7 +22559,7 @@
     </x:row>
     <x:row r="648" ht="20" customHeight="1">
       <x:c r="A648" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B648" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -22592,7 +22592,7 @@
     </x:row>
     <x:row r="649" ht="20" customHeight="1">
       <x:c r="A649" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B649" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -22625,7 +22625,7 @@
     </x:row>
     <x:row r="650" ht="20" customHeight="1">
       <x:c r="A650" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B650" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -22658,7 +22658,7 @@
     </x:row>
     <x:row r="651" ht="20" customHeight="1">
       <x:c r="A651" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B651" s="2" t="str">
         <x:v>Muse</x:v>
@@ -22691,7 +22691,7 @@
     </x:row>
     <x:row r="652" ht="20" customHeight="1">
       <x:c r="A652" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B652" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -22724,7 +22724,7 @@
     </x:row>
     <x:row r="653" ht="20" customHeight="1">
       <x:c r="A653" s="7" t="d">
-        <x:v>2026-09-11T12:00:00.000Z</x:v>
+        <x:v>2026-09-11T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B653" s="2" t="str">
         <x:v>Trail</x:v>
@@ -22757,7 +22757,7 @@
     </x:row>
     <x:row r="654" ht="20" customHeight="1">
       <x:c r="A654" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B654" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -22790,7 +22790,7 @@
     </x:row>
     <x:row r="655" ht="20" customHeight="1">
       <x:c r="A655" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B655" s="2" t="str">
         <x:v>Stride</x:v>
@@ -22823,7 +22823,7 @@
     </x:row>
     <x:row r="656" ht="20" customHeight="1">
       <x:c r="A656" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B656" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -22856,7 +22856,7 @@
     </x:row>
     <x:row r="657" ht="20" customHeight="1">
       <x:c r="A657" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B657" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -22889,7 +22889,7 @@
     </x:row>
     <x:row r="658" ht="20" customHeight="1">
       <x:c r="A658" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B658" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -22922,7 +22922,7 @@
     </x:row>
     <x:row r="659" ht="20" customHeight="1">
       <x:c r="A659" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B659" s="2" t="str">
         <x:v>Muse</x:v>
@@ -22955,7 +22955,7 @@
     </x:row>
     <x:row r="660" ht="20" customHeight="1">
       <x:c r="A660" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B660" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -22988,7 +22988,7 @@
     </x:row>
     <x:row r="661" ht="20" customHeight="1">
       <x:c r="A661" s="7" t="d">
-        <x:v>2026-09-12T12:00:00.000Z</x:v>
+        <x:v>2026-09-12T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B661" s="2" t="str">
         <x:v>Trail</x:v>
@@ -23021,7 +23021,7 @@
     </x:row>
     <x:row r="662" ht="20" customHeight="1">
       <x:c r="A662" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B662" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -23054,7 +23054,7 @@
     </x:row>
     <x:row r="663" ht="20" customHeight="1">
       <x:c r="A663" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B663" s="2" t="str">
         <x:v>Stride</x:v>
@@ -23087,7 +23087,7 @@
     </x:row>
     <x:row r="664" ht="20" customHeight="1">
       <x:c r="A664" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B664" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -23120,7 +23120,7 @@
     </x:row>
     <x:row r="665" ht="20" customHeight="1">
       <x:c r="A665" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B665" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -23153,7 +23153,7 @@
     </x:row>
     <x:row r="666" ht="20" customHeight="1">
       <x:c r="A666" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B666" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -23186,7 +23186,7 @@
     </x:row>
     <x:row r="667" ht="20" customHeight="1">
       <x:c r="A667" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B667" s="2" t="str">
         <x:v>Muse</x:v>
@@ -23219,7 +23219,7 @@
     </x:row>
     <x:row r="668" ht="20" customHeight="1">
       <x:c r="A668" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B668" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -23252,7 +23252,7 @@
     </x:row>
     <x:row r="669" ht="20" customHeight="1">
       <x:c r="A669" s="7" t="d">
-        <x:v>2026-09-13T12:00:00.000Z</x:v>
+        <x:v>2026-09-13T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B669" s="2" t="str">
         <x:v>Trail</x:v>
@@ -23285,7 +23285,7 @@
     </x:row>
     <x:row r="670" ht="20" customHeight="1">
       <x:c r="A670" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B670" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -23318,7 +23318,7 @@
     </x:row>
     <x:row r="671" ht="20" customHeight="1">
       <x:c r="A671" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B671" s="2" t="str">
         <x:v>Stride</x:v>
@@ -23351,7 +23351,7 @@
     </x:row>
     <x:row r="672" ht="20" customHeight="1">
       <x:c r="A672" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B672" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -23384,7 +23384,7 @@
     </x:row>
     <x:row r="673" ht="20" customHeight="1">
       <x:c r="A673" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B673" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -23417,7 +23417,7 @@
     </x:row>
     <x:row r="674" ht="20" customHeight="1">
       <x:c r="A674" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B674" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -23450,7 +23450,7 @@
     </x:row>
     <x:row r="675" ht="20" customHeight="1">
       <x:c r="A675" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B675" s="2" t="str">
         <x:v>Muse</x:v>
@@ -23483,7 +23483,7 @@
     </x:row>
     <x:row r="676" ht="20" customHeight="1">
       <x:c r="A676" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B676" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -23516,7 +23516,7 @@
     </x:row>
     <x:row r="677" ht="20" customHeight="1">
       <x:c r="A677" s="7" t="d">
-        <x:v>2026-09-14T12:00:00.000Z</x:v>
+        <x:v>2026-09-14T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B677" s="2" t="str">
         <x:v>Trail</x:v>
@@ -23549,7 +23549,7 @@
     </x:row>
     <x:row r="678" ht="20" customHeight="1">
       <x:c r="A678" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B678" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -23582,7 +23582,7 @@
     </x:row>
     <x:row r="679" ht="20" customHeight="1">
       <x:c r="A679" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B679" s="2" t="str">
         <x:v>Stride</x:v>
@@ -23615,7 +23615,7 @@
     </x:row>
     <x:row r="680" ht="20" customHeight="1">
       <x:c r="A680" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B680" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -23648,7 +23648,7 @@
     </x:row>
     <x:row r="681" ht="20" customHeight="1">
       <x:c r="A681" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B681" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -23681,7 +23681,7 @@
     </x:row>
     <x:row r="682" ht="20" customHeight="1">
       <x:c r="A682" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B682" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -23714,7 +23714,7 @@
     </x:row>
     <x:row r="683" ht="20" customHeight="1">
       <x:c r="A683" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B683" s="2" t="str">
         <x:v>Muse</x:v>
@@ -23747,7 +23747,7 @@
     </x:row>
     <x:row r="684" ht="20" customHeight="1">
       <x:c r="A684" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B684" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -23780,7 +23780,7 @@
     </x:row>
     <x:row r="685" ht="20" customHeight="1">
       <x:c r="A685" s="7" t="d">
-        <x:v>2026-09-15T12:00:00.000Z</x:v>
+        <x:v>2026-09-15T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B685" s="2" t="str">
         <x:v>Trail</x:v>
@@ -23813,7 +23813,7 @@
     </x:row>
     <x:row r="686" ht="20" customHeight="1">
       <x:c r="A686" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B686" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -23846,7 +23846,7 @@
     </x:row>
     <x:row r="687" ht="20" customHeight="1">
       <x:c r="A687" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B687" s="2" t="str">
         <x:v>Stride</x:v>
@@ -23879,7 +23879,7 @@
     </x:row>
     <x:row r="688" ht="20" customHeight="1">
       <x:c r="A688" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B688" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -23912,7 +23912,7 @@
     </x:row>
     <x:row r="689" ht="20" customHeight="1">
       <x:c r="A689" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B689" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -23945,7 +23945,7 @@
     </x:row>
     <x:row r="690" ht="20" customHeight="1">
       <x:c r="A690" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B690" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -23978,7 +23978,7 @@
     </x:row>
     <x:row r="691" ht="20" customHeight="1">
       <x:c r="A691" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B691" s="2" t="str">
         <x:v>Muse</x:v>
@@ -24011,7 +24011,7 @@
     </x:row>
     <x:row r="692" ht="20" customHeight="1">
       <x:c r="A692" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B692" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -24044,7 +24044,7 @@
     </x:row>
     <x:row r="693" ht="20" customHeight="1">
       <x:c r="A693" s="7" t="d">
-        <x:v>2026-09-16T12:00:00.000Z</x:v>
+        <x:v>2026-09-16T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B693" s="2" t="str">
         <x:v>Trail</x:v>
@@ -24077,7 +24077,7 @@
     </x:row>
     <x:row r="694" ht="20" customHeight="1">
       <x:c r="A694" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B694" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -24110,7 +24110,7 @@
     </x:row>
     <x:row r="695" ht="20" customHeight="1">
       <x:c r="A695" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B695" s="2" t="str">
         <x:v>Stride</x:v>
@@ -24143,7 +24143,7 @@
     </x:row>
     <x:row r="696" ht="20" customHeight="1">
       <x:c r="A696" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B696" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -24176,7 +24176,7 @@
     </x:row>
     <x:row r="697" ht="20" customHeight="1">
       <x:c r="A697" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B697" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -24209,7 +24209,7 @@
     </x:row>
     <x:row r="698" ht="20" customHeight="1">
       <x:c r="A698" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B698" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -24242,7 +24242,7 @@
     </x:row>
     <x:row r="699" ht="20" customHeight="1">
       <x:c r="A699" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B699" s="2" t="str">
         <x:v>Muse</x:v>
@@ -24275,7 +24275,7 @@
     </x:row>
     <x:row r="700" ht="20" customHeight="1">
       <x:c r="A700" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B700" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -24308,7 +24308,7 @@
     </x:row>
     <x:row r="701" ht="20" customHeight="1">
       <x:c r="A701" s="7" t="d">
-        <x:v>2026-09-17T12:00:00.000Z</x:v>
+        <x:v>2026-09-17T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B701" s="2" t="str">
         <x:v>Trail</x:v>
@@ -24341,7 +24341,7 @@
     </x:row>
     <x:row r="702" ht="20" customHeight="1">
       <x:c r="A702" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B702" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -24374,7 +24374,7 @@
     </x:row>
     <x:row r="703" ht="20" customHeight="1">
       <x:c r="A703" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B703" s="2" t="str">
         <x:v>Stride</x:v>
@@ -24407,7 +24407,7 @@
     </x:row>
     <x:row r="704" ht="20" customHeight="1">
       <x:c r="A704" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B704" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -24440,7 +24440,7 @@
     </x:row>
     <x:row r="705" ht="20" customHeight="1">
       <x:c r="A705" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B705" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -24473,7 +24473,7 @@
     </x:row>
     <x:row r="706" ht="20" customHeight="1">
       <x:c r="A706" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B706" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -24506,7 +24506,7 @@
     </x:row>
     <x:row r="707" ht="20" customHeight="1">
       <x:c r="A707" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B707" s="2" t="str">
         <x:v>Muse</x:v>
@@ -24539,7 +24539,7 @@
     </x:row>
     <x:row r="708" ht="20" customHeight="1">
       <x:c r="A708" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B708" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -24572,7 +24572,7 @@
     </x:row>
     <x:row r="709" ht="20" customHeight="1">
       <x:c r="A709" s="7" t="d">
-        <x:v>2026-09-18T12:00:00.000Z</x:v>
+        <x:v>2026-09-18T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B709" s="2" t="str">
         <x:v>Trail</x:v>
@@ -24605,7 +24605,7 @@
     </x:row>
     <x:row r="710" ht="20" customHeight="1">
       <x:c r="A710" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B710" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -24638,7 +24638,7 @@
     </x:row>
     <x:row r="711" ht="20" customHeight="1">
       <x:c r="A711" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B711" s="2" t="str">
         <x:v>Stride</x:v>
@@ -24671,7 +24671,7 @@
     </x:row>
     <x:row r="712" ht="20" customHeight="1">
       <x:c r="A712" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B712" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -24704,7 +24704,7 @@
     </x:row>
     <x:row r="713" ht="20" customHeight="1">
       <x:c r="A713" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B713" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -24737,7 +24737,7 @@
     </x:row>
     <x:row r="714" ht="20" customHeight="1">
       <x:c r="A714" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B714" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -24770,7 +24770,7 @@
     </x:row>
     <x:row r="715" ht="20" customHeight="1">
       <x:c r="A715" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B715" s="2" t="str">
         <x:v>Muse</x:v>
@@ -24803,7 +24803,7 @@
     </x:row>
     <x:row r="716" ht="20" customHeight="1">
       <x:c r="A716" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B716" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -24836,7 +24836,7 @@
     </x:row>
     <x:row r="717" ht="20" customHeight="1">
       <x:c r="A717" s="7" t="d">
-        <x:v>2026-09-19T12:00:00.000Z</x:v>
+        <x:v>2026-09-19T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B717" s="2" t="str">
         <x:v>Trail</x:v>
@@ -24869,7 +24869,7 @@
     </x:row>
     <x:row r="718" ht="20" customHeight="1">
       <x:c r="A718" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B718" s="2" t="str">
         <x:v>LingoLoop</x:v>
@@ -24902,7 +24902,7 @@
     </x:row>
     <x:row r="719" ht="20" customHeight="1">
       <x:c r="A719" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B719" s="2" t="str">
         <x:v>Stride</x:v>
@@ -24935,7 +24935,7 @@
     </x:row>
     <x:row r="720" ht="20" customHeight="1">
       <x:c r="A720" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B720" s="2" t="str">
         <x:v>Ledger</x:v>
@@ -24968,7 +24968,7 @@
     </x:row>
     <x:row r="721" ht="20" customHeight="1">
       <x:c r="A721" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B721" s="2" t="str">
         <x:v>Mealwise</x:v>
@@ -25001,7 +25001,7 @@
     </x:row>
     <x:row r="722" ht="20" customHeight="1">
       <x:c r="A722" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B722" s="2" t="str">
         <x:v>Orbit</x:v>
@@ -25034,7 +25034,7 @@
     </x:row>
     <x:row r="723" ht="20" customHeight="1">
       <x:c r="A723" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B723" s="2" t="str">
         <x:v>Muse</x:v>
@@ -25067,7 +25067,7 @@
     </x:row>
     <x:row r="724" ht="20" customHeight="1">
       <x:c r="A724" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B724" s="2" t="str">
         <x:v>FocusFlow</x:v>
@@ -25100,7 +25100,7 @@
     </x:row>
     <x:row r="725" ht="20" customHeight="1">
       <x:c r="A725" s="7" t="d">
-        <x:v>2026-09-20T12:00:00.000Z</x:v>
+        <x:v>2026-09-20T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="B725" s="2" t="str">
         <x:v>Trail</x:v>
@@ -25134,7 +25134,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b80fd21ab344f11"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9814c8b5f36646b4"/>
   </x:tableParts>
 </x:worksheet>
 </file>